--- a/文案總表.xlsx
+++ b/文案總表.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄外抓捕</t>
+          <t xml:space="preserve">探監</t>
         </is>
       </c>
       <c r="E27"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">移監劇場</t>
+          <t xml:space="preserve">慰問服刑友人</t>
         </is>
       </c>
       <c r="E28"/>
@@ -740,7 +740,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">30W</t>
+          <t xml:space="preserve">10W</t>
         </is>
       </c>
       <c r="E29"/>
@@ -763,7 +763,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">起</t>
+          <t xml:space="preserve">/ 人</t>
         </is>
       </c>
       <c r="E30"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">想把朋友抓進監獄？由委託人下單付費，獄卒出動至指定地點，上演約 15 分鐘逮捕劇場（白頻演出）。</t>
+          <t xml:space="preserve">探望正在服刑中的囚犯朋友。不佔囚犯名額，限當梯次營業時間內。</t>
         </is>
       </c>
       <c r="E31"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 名獄卒出動 30W ／ 3 名 45W ／ 4 名 60W，每追加 1 人 +15W</t>
+          <t xml:space="preserve">探監合照 ×1：在鐵欄內外與囚犯、獄卒合照</t>
         </is>
       </c>
       <c r="E32"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">需當事人配合前往店舖</t>
+          <t xml:space="preserve">探監留言：替囚犯留下一段話，記入後台資料</t>
         </is>
       </c>
       <c r="E33"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">不論最終是否到店，移監費皆不退還</t>
+          <t xml:space="preserve">慰問品互動：指定一名獄卒對囚犯即興演出（鼓勵系／責罵系）</t>
         </is>
       </c>
       <c r="E34"/>
@@ -868,17 +868,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目B+A·名稱</t>
+          <t xml:space="preserve">價目B·項目4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓捕＋入獄套餐</t>
+          <t xml:space="preserve">進階客製化演出（如整人劇場、假裝放人結果沒有）可加購 5W</t>
         </is>
       </c>
       <c r="E35"/>
@@ -891,17 +891,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目B+A·副標</t>
+          <t xml:space="preserve">價目C·名稱</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">一網打盡</t>
+          <t xml:space="preserve">刑期延長</t>
         </is>
       </c>
       <c r="E36"/>
@@ -914,17 +914,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目B+A·價格</t>
+          <t xml:space="preserve">價目C·副標</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">70W</t>
+          <t xml:space="preserve">自願續刑</t>
         </is>
       </c>
       <c r="E37"/>
@@ -937,17 +937,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目B+A·原價</t>
+          <t xml:space="preserve">價目C·價格</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">80W</t>
+          <t xml:space="preserve">10W</t>
         </is>
       </c>
       <c r="E38"/>
@@ -965,12 +965,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目B+A·說明</t>
+          <t xml:space="preserve">價目C·單位</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">委託人一次包下「抓捕 2 人出動 ＋ 被捕者入獄費」，套餐省 10W。</t>
+          <t xml:space="preserve">/ hr</t>
         </is>
       </c>
       <c r="E39"/>
@@ -983,17 +983,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目B+A·項目1</t>
+          <t xml:space="preserve">價目C·說明</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">被捕者保釋金制度照常運作</t>
+          <t xml:space="preserve">2 小時刑期結束後，可申請自願續刑或由獄卒判定加刑（RP 演出）。</t>
         </is>
       </c>
       <c r="E40"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目B+A·項目2</t>
+          <t xml:space="preserve">價目C·項目1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">費用分攤由委託人與被捕者自行協商</t>
+          <t xml:space="preserve">視獄卒排班狀況開放，不保證每次可用</t>
         </is>
       </c>
       <c r="E41"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目B+A·項目3</t>
+          <t xml:space="preserve">價目C·項目2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">抓捕需 3 人以上出動：套餐底價 70W ＋ 超出獄卒費（每 +1 人 +15W）</t>
+          <t xml:space="preserve">延長時段的進度同樣計入保釋金判定，可逆轉結果</t>
         </is>
       </c>
       <c r="E42"/>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目C·名稱</t>
+          <t xml:space="preserve">加購1·名稱</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">探監</t>
+          <t xml:space="preserve">監獄外抓捕</t>
         </is>
       </c>
       <c r="E43"/>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目C·副標</t>
+          <t xml:space="preserve">加購1·價格</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">慰問服刑友人</t>
+          <t xml:space="preserve">30W 起</t>
         </is>
       </c>
       <c r="E44"/>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目C·價格</t>
+          <t xml:space="preserve">加購1·說明</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">10W</t>
+          <t xml:space="preserve">想把朋友抓進監獄？委託人下單付費，獄卒出動至指定地點上演約 15 分鐘逮捕劇場（白頻演出）。2 名獄卒 30W，每追加 1 人 +15W；被捕者入獄費另計，需當事人配合前往店舖，不論是否到店費用不退還</t>
         </is>
       </c>
       <c r="E45"/>
@@ -1121,17 +1121,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目C·單位</t>
+          <t xml:space="preserve">加購2·名稱</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ 人</t>
+          <t xml:space="preserve">拍立得合照</t>
         </is>
       </c>
       <c r="E46"/>
@@ -1144,17 +1144,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目C·說明</t>
+          <t xml:space="preserve">加購2·價格</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">探望正在服刑中的囚犯朋友。不佔囚犯名額，限當梯次營業時間內。</t>
+          <t xml:space="preserve">5W / 張</t>
         </is>
       </c>
       <c r="E47"/>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目C·項目1</t>
+          <t xml:space="preserve">加購2·說明</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">探監合照 ×1：在鐵欄內外與囚犯、獄卒合照</t>
+          <t xml:space="preserve">與指定獄卒合照，含手寫簽名小卡；限完成目標的囚犯購買</t>
         </is>
       </c>
       <c r="E48"/>
@@ -1190,17 +1190,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目C·項目2</t>
+          <t xml:space="preserve">加購3·名稱</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">探監留言：替囚犯留下一段話，記入後台資料</t>
+          <t xml:space="preserve">入獄肖像照</t>
         </is>
       </c>
       <c r="E49"/>
@@ -1213,17 +1213,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目C·項目3</t>
+          <t xml:space="preserve">加購3·價格</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">慰問品互動：指定一名獄卒對囚犯即興演出（鼓勵系／責罵系）</t>
+          <t xml:space="preserve">80W</t>
         </is>
       </c>
       <c r="E50"/>
@@ -1236,17 +1236,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目C·項目4</t>
+          <t xml:space="preserve">加購3·說明</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">進階客製化演出（如整人劇場、假裝放人結果沒有）可加購 5W</t>
+          <t xml:space="preserve">入獄紀念肖像照</t>
         </is>
       </c>
       <c r="E51"/>
@@ -1259,17 +1259,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">58</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目D·名稱</t>
+          <t xml:space="preserve">場次徽章·預約中</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">刑期延長</t>
+          <t xml:space="preserve">預約中</t>
         </is>
       </c>
       <c r="E52"/>
@@ -1282,17 +1282,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目D·副標</t>
+          <t xml:space="preserve">場次徽章·報名暫停</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">自願續刑</t>
+          <t xml:space="preserve">報名暫停</t>
         </is>
       </c>
       <c r="E53"/>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目D·價格</t>
+          <t xml:space="preserve">場次徽章·入場中</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">10W</t>
+          <t xml:space="preserve">入場中</t>
         </is>
       </c>
       <c r="E54"/>
@@ -1328,17 +1328,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目D·單位</t>
+          <t xml:space="preserve">場次徽章·服刑中</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ hr</t>
+          <t xml:space="preserve">服刑中</t>
         </is>
       </c>
       <c r="E55"/>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">116</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目D·說明</t>
+          <t xml:space="preserve">人員·角色</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 小時刑期結束後，可申請自願續刑或由獄卒判定加刑（RP 演出）。</t>
+          <t xml:space="preserve">典獄長 / 獄卒</t>
         </is>
       </c>
       <c r="E56"/>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">117</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目D·項目1</t>
+          <t xml:space="preserve">人員·名稱 fallback</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">視獄卒排班狀況開放，不保證每次可用</t>
+          <t xml:space="preserve">——</t>
         </is>
       </c>
       <c r="E57"/>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">199</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">價目D·項目2</t>
+          <t xml:space="preserve">系統訊息·收監成功</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">延長時段的進度同樣計入保釋金判定，可逆轉結果</t>
+          <t xml:space="preserve">收監成功。鈴響時見。</t>
         </is>
       </c>
       <c r="E58"/>
@@ -1420,17 +1420,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">200</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">加購1·名稱</t>
+          <t xml:space="preserve">系統訊息·已報名</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">拍立得合照</t>
+          <t xml:space="preserve">你已在此梯次服刑名冊上。</t>
         </is>
       </c>
       <c r="E59"/>
@@ -1443,17 +1443,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">加購1·價格</t>
+          <t xml:space="preserve">系統訊息·已停收監</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5W / 張</t>
+          <t xml:space="preserve">此梯次已停止收監。</t>
         </is>
       </c>
       <c r="E60"/>
@@ -1466,17 +1466,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">202</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">加購1·說明</t>
+          <t xml:space="preserve">系統訊息·未登入</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">與指定獄卒合照，含手寫簽名小卡；限完成目標的囚犯購買</t>
+          <t xml:space="preserve">請先以 Discord 登入。</t>
         </is>
       </c>
       <c r="E61"/>
@@ -1489,17 +1489,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">203</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">加購2·名稱</t>
+          <t xml:space="preserve">系統訊息·收監失敗</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">入獄肖像照</t>
+          <t xml:space="preserve">收監失敗，請稍後再試。</t>
         </is>
       </c>
       <c r="E62"/>
@@ -1512,17 +1512,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">212</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">加購2·價格</t>
+          <t xml:space="preserve">系統訊息·取消確認</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">80W</t>
+          <t xml:space="preserve">確定取消本梯次預約？</t>
         </is>
       </c>
       <c r="E63"/>
@@ -1535,17 +1535,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">216</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">加購2·說明</t>
+          <t xml:space="preserve">系統訊息·已取消/取消失敗</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">入獄紀念肖像照</t>
+          <t xml:space="preserve">已取消預約。 / 取消失敗，請稍後再試。</t>
         </is>
       </c>
       <c r="E64"/>
@@ -1558,17 +1558,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">222</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次徽章·預約中</t>
+          <t xml:space="preserve">系統訊息·已停收監</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">預約中</t>
+          <t xml:space="preserve">此梯次已停止收監。</t>
         </is>
       </c>
       <c r="E65"/>
@@ -1581,17 +1581,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t xml:space="preserve">226</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次徽章·報名暫停</t>
+          <t xml:space="preserve">系統訊息·重新報名失敗/成功</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">報名暫停</t>
+          <t xml:space="preserve">重新報名失敗，請稍後再試。 / 已重新登記入監名冊。</t>
         </is>
       </c>
       <c r="E66"/>
@@ -1604,17 +1604,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">238</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次徽章·入場中</t>
+          <t xml:space="preserve">導覽·品牌</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">入場中</t>
+          <t xml:space="preserve">死線監獄</t>
         </is>
       </c>
       <c r="E67"/>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">78</t>
+          <t xml:space="preserve">240</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次徽章·服刑中</t>
+          <t xml:space="preserve">導覽·選單</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑中</t>
+          <t xml:space="preserve">服刑須知</t>
         </is>
       </c>
       <c r="E68"/>
@@ -1650,17 +1650,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">133</t>
+          <t xml:space="preserve">241</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">人員·角色</t>
+          <t xml:space="preserve">導覽·選單</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">典獄長 / 獄卒</t>
+          <t xml:space="preserve">監獄人員</t>
         </is>
       </c>
       <c r="E69"/>
@@ -1673,17 +1673,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">134</t>
+          <t xml:space="preserve">242</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">人員·名稱 fallback</t>
+          <t xml:space="preserve">導覽·選單</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">——</t>
+          <t xml:space="preserve">犯人牆</t>
         </is>
       </c>
       <c r="E70"/>
@@ -1696,17 +1696,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">216</t>
+          <t xml:space="preserve">243</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·收監成功</t>
+          <t xml:space="preserve">導覽·選單</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">收監成功。鈴響時見。</t>
+          <t xml:space="preserve">名人堂</t>
         </is>
       </c>
       <c r="E71"/>
@@ -1719,17 +1719,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">217</t>
+          <t xml:space="preserve">244</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·已報名</t>
+          <t xml:space="preserve">導覽·選單</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">你已在此梯次服刑名冊上。</t>
+          <t xml:space="preserve">收費價目</t>
         </is>
       </c>
       <c r="E72"/>
@@ -1742,17 +1742,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">218</t>
+          <t xml:space="preserve">245</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·已停收監</t>
+          <t xml:space="preserve">導覽·選單</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">此梯次已停止收監。</t>
+          <t xml:space="preserve">趕稿場次</t>
         </is>
       </c>
       <c r="E73"/>
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">219</t>
+          <t xml:space="preserve">248</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·未登入</t>
+          <t xml:space="preserve">導覽·系統入口</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">請先以 Discord 登入。</t>
+          <t xml:space="preserve">ACCESS · 監獄系統</t>
         </is>
       </c>
       <c r="E74"/>
@@ -1788,17 +1788,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">220</t>
+          <t xml:space="preserve">249</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·收監失敗</t>
+          <t xml:space="preserve">導覽·Discord aria</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">收監失敗，請稍後再試。</t>
+          <t xml:space="preserve">Discord</t>
         </is>
       </c>
       <c r="E75"/>
@@ -1811,17 +1811,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">229</t>
+          <t xml:space="preserve">258</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·取消確認</t>
+          <t xml:space="preserve">漢堡·aria</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">確定取消本梯次預約？</t>
+          <t xml:space="preserve">選單</t>
         </is>
       </c>
       <c r="E76"/>
@@ -1834,17 +1834,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">233</t>
+          <t xml:space="preserve">273</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·已取消/取消失敗</t>
+          <t xml:space="preserve">抽屜選單</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">已取消預約。 / 取消失敗，請稍後再試。</t>
+          <t xml:space="preserve">服刑須知</t>
         </is>
       </c>
       <c r="E77"/>
@@ -1857,17 +1857,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">239</t>
+          <t xml:space="preserve">273</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·已停收監</t>
+          <t xml:space="preserve">抽屜選單</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">此梯次已停止收監。</t>
+          <t xml:space="preserve">監獄人員</t>
         </is>
       </c>
       <c r="E78"/>
@@ -1880,17 +1880,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">243</t>
+          <t xml:space="preserve">273</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·重新報名失敗/成功</t>
+          <t xml:space="preserve">抽屜選單</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">重新報名失敗，請稍後再試。 / 已重新登記入監名冊。</t>
+          <t xml:space="preserve">犯人牆</t>
         </is>
       </c>
       <c r="E79"/>
@@ -1903,17 +1903,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">255</t>
+          <t xml:space="preserve">274</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·品牌</t>
+          <t xml:space="preserve">抽屜選單</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">死線監獄</t>
+          <t xml:space="preserve">名人堂</t>
         </is>
       </c>
       <c r="E80"/>
@@ -1926,17 +1926,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">257</t>
+          <t xml:space="preserve">274</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·選單</t>
+          <t xml:space="preserve">抽屜選單</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知</t>
+          <t xml:space="preserve">收費價目</t>
         </is>
       </c>
       <c r="E81"/>
@@ -1949,17 +1949,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">258</t>
+          <t xml:space="preserve">274</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·選單</t>
+          <t xml:space="preserve">抽屜選單</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員</t>
+          <t xml:space="preserve">趕稿場次</t>
         </is>
       </c>
       <c r="E82"/>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">259</t>
+          <t xml:space="preserve">284</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·選單</t>
+          <t xml:space="preserve">Hero·收容徽章</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆</t>
+          <t xml:space="preserve">收容中 · INTAKE OPEN · 24H</t>
         </is>
       </c>
       <c r="E83"/>
@@ -1995,17 +1995,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">260</t>
+          <t xml:space="preserve">285</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·選單</t>
+          <t xml:space="preserve">Hero·主標</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂</t>
+          <t xml:space="preserve">死線監獄</t>
         </is>
       </c>
       <c r="E84"/>
@@ -2018,17 +2018,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">261</t>
+          <t xml:space="preserve">286</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·選單</t>
+          <t xml:space="preserve">Hero·編號條</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目</t>
+          <t xml:space="preserve">DEADLINE PRISON · NO.0118</t>
         </is>
       </c>
       <c r="E85"/>
@@ -2041,17 +2041,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">262</t>
+          <t xml:space="preserve">287</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·選單</t>
+          <t xml:space="preserve">Hero·標語</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次</t>
+          <t xml:space="preserve">把自己關進來，服完這一頁死線。沒有逃獄，只有交稿。</t>
         </is>
       </c>
       <c r="E86"/>
@@ -2064,17 +2064,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">265</t>
+          <t xml:space="preserve">288</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·系統入口</t>
+          <t xml:space="preserve">Hero·拘留登記 aria</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACCESS · 監獄系統</t>
+          <t xml:space="preserve">拘留登記</t>
         </is>
       </c>
       <c r="E87"/>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">266</t>
+          <t xml:space="preserve">289</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·Discord aria</t>
+          <t xml:space="preserve">Hero·拘留卡</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discord</t>
+          <t xml:space="preserve">罪名／慣性拖稿</t>
         </is>
       </c>
       <c r="E88"/>
@@ -2110,17 +2110,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">275</t>
+          <t xml:space="preserve">290</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">漢堡·aria</t>
+          <t xml:space="preserve">Hero·拘留卡</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">選單</t>
+          <t xml:space="preserve">刑期／一個番茄鐘起</t>
         </is>
       </c>
       <c r="E89"/>
@@ -2133,17 +2133,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">290</t>
+          <t xml:space="preserve">291</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">抽屜選單</t>
+          <t xml:space="preserve">Hero·拘留卡</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知</t>
+          <t xml:space="preserve">保釋／不受理</t>
         </is>
       </c>
       <c r="E90"/>
@@ -2156,17 +2156,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">290</t>
+          <t xml:space="preserve">294</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">抽屜選單</t>
+          <t xml:space="preserve">Hero·主CTA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員</t>
+          <t xml:space="preserve">入監服刑 ▸</t>
         </is>
       </c>
       <c r="E91"/>
@@ -2179,17 +2179,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">290</t>
+          <t xml:space="preserve">296</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">抽屜選單</t>
+          <t xml:space="preserve">Hero·滾動提示</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆</t>
+          <t xml:space="preserve">▼ 向下了解服刑流程</t>
         </is>
       </c>
       <c r="E92"/>
@@ -2202,17 +2202,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">303</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">抽屜選單</t>
+          <t xml:space="preserve">服刑須知·eyebrow</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂</t>
+          <t xml:space="preserve">服刑須知 // BLOCK 01</t>
         </is>
       </c>
       <c r="E93"/>
@@ -2225,17 +2225,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">304</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">抽屜選單</t>
+          <t xml:space="preserve">服刑須知·標題</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目</t>
+          <t xml:space="preserve">這裡關的，是趕不完稿的人</t>
         </is>
       </c>
       <c r="E94"/>
@@ -2248,17 +2248,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">305</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">抽屜選單</t>
+          <t xml:space="preserve">服刑須知·說明</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次</t>
+          <t xml:space="preserve">死線監獄是一間以「番茄鐘」執行的趕稿收容所。入監即上鎖，鈴響才放風，全程同步直播犯人服刑進度——你不是一個人在趕，是一群人一起服刑。</t>
         </is>
       </c>
       <c r="E95"/>
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">301</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·收容徽章</t>
+          <t xml:space="preserve">服刑須知·地點</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">收容中 · INTAKE OPEN · 24H</t>
+          <t xml:space="preserve">服刑地點：巴哈姆特 - 薰衣草苗園 - 1區 - 18號</t>
         </is>
       </c>
       <c r="E96"/>
@@ -2294,17 +2294,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">302</t>
+          <t xml:space="preserve">313</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·主標</t>
+          <t xml:space="preserve">服刑須知·節奏標題</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">死線監獄</t>
+          <t xml:space="preserve">服刑節奏 · POMODORO CYCLE</t>
         </is>
       </c>
       <c r="E97"/>
@@ -2317,17 +2317,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">303</t>
+          <t xml:space="preserve">319</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·編號條</t>
+          <t xml:space="preserve">服刑須知·圖例</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEADLINE PRISON · NO.0118</t>
+          <t xml:space="preserve">專注 25 分</t>
         </is>
       </c>
       <c r="E98"/>
@@ -2340,17 +2340,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">304</t>
+          <t xml:space="preserve">320</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·標語</t>
+          <t xml:space="preserve">服刑須知·圖例</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">把自己關進來，服完這一頁死線。沒有逃獄，只有交稿。</t>
+          <t xml:space="preserve">放風 5 分</t>
         </is>
       </c>
       <c r="E99"/>
@@ -2363,17 +2363,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">305</t>
+          <t xml:space="preserve">321</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·拘留登記 aria</t>
+          <t xml:space="preserve">服刑須知·圖例</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">拘留登記</t>
+          <t xml:space="preserve">長休 15 分（每 4 輪）</t>
         </is>
       </c>
       <c r="E100"/>
@@ -2386,17 +2386,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">330</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·拘留卡</t>
+          <t xml:space="preserve">監獄人員·eyebrow</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">罪名／慣性拖稿</t>
+          <t xml:space="preserve">獄方名冊 // BLOCK 02</t>
         </is>
       </c>
       <c r="E101"/>
@@ -2409,17 +2409,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">307</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·拘留卡</t>
+          <t xml:space="preserve">監獄人員·標題</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">刑期／一個番茄鐘起</t>
+          <t xml:space="preserve">監獄人員</t>
         </is>
       </c>
       <c r="E102"/>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">308</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·拘留卡</t>
+          <t xml:space="preserve">監獄人員·說明</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">保釋／不受理</t>
+          <t xml:space="preserve">看守這座監獄、確保沒人逃稿的人。</t>
         </is>
       </c>
       <c r="E103"/>
@@ -2455,17 +2455,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311</t>
+          <t xml:space="preserve">334</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·主CTA</t>
+          <t xml:space="preserve">監獄人員·空狀態</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監服刑 ▸</t>
+          <t xml:space="preserve">名冊整備中…</t>
         </is>
       </c>
       <c r="E104"/>
@@ -2478,17 +2478,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">313</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·滾動提示</t>
+          <t xml:space="preserve">自介 fallback(人員/犯人)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">▼ 向下了解服刑流程</t>
+          <t xml:space="preserve">〔機密資料未公開〕</t>
         </is>
       </c>
       <c r="E105"/>
@@ -2501,17 +2501,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">320</t>
+          <t xml:space="preserve">353</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·eyebrow</t>
+          <t xml:space="preserve">犯人牆·eyebrow</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知 // BLOCK 01</t>
+          <t xml:space="preserve">服刑紀錄 // BLOCK 03</t>
         </is>
       </c>
       <c r="E106"/>
@@ -2524,17 +2524,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">354</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·標題</t>
+          <t xml:space="preserve">犯人牆·標題</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">這裡關的，是趕不完稿的人</t>
+          <t xml:space="preserve">犯人牆</t>
         </is>
       </c>
       <c r="E107"/>
@@ -2547,17 +2547,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">355</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·說明</t>
+          <t xml:space="preserve">犯人牆·說明</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">死線監獄是一間以「番茄鐘」執行的趕稿收容所。入監即上鎖，鈴響才放風，全程同步直播犯人服刑進度——你不是一個人在趕，是一群人一起服刑。</t>
+          <t xml:space="preserve">自願把服刑紀錄公開示眾的犯人。沒被趕完的稿，大家一起看著。</t>
         </is>
       </c>
       <c r="E108"/>
@@ -2570,17 +2570,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">357</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·地點</t>
+          <t xml:space="preserve">犯人牆·載入中</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑地點：巴哈姆特 - 薰衣草苗園 - 1區 - 18號</t>
+          <t xml:space="preserve">調閱服刑紀錄中…</t>
         </is>
       </c>
       <c r="E109"/>
@@ -2593,17 +2593,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">330</t>
+          <t xml:space="preserve">358</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·節奏標題</t>
+          <t xml:space="preserve">犯人牆·空狀態</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑節奏 · POMODORO CYCLE</t>
+          <t xml:space="preserve">目前無人願意公開服刑紀錄</t>
         </is>
       </c>
       <c r="E110"/>
@@ -2616,17 +2616,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">336</t>
+          <t xml:space="preserve">378</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·圖例</t>
+          <t xml:space="preserve">名人堂·eyebrow</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">專注 25 分</t>
+          <t xml:space="preserve">監獄名人堂 // BLOCK 04</t>
         </is>
       </c>
       <c r="E111"/>
@@ -2639,17 +2639,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">337</t>
+          <t xml:space="preserve">379</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·圖例</t>
+          <t xml:space="preserve">名人堂·標題</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">放風 5 分</t>
+          <t xml:space="preserve">名人堂</t>
         </is>
       </c>
       <c r="E112"/>
@@ -2662,17 +2662,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">338</t>
+          <t xml:space="preserve">380</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·圖例</t>
+          <t xml:space="preserve">名人堂·說明</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">長休 15 分（每 4 輪）</t>
+          <t xml:space="preserve">服刑最勤、人氣最高的犯人。次數照實計入，名字是否公開由本人決定。</t>
         </is>
       </c>
       <c r="E113"/>
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">347</t>
+          <t xml:space="preserve">383</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員·eyebrow</t>
+          <t xml:space="preserve">名人堂·榜一</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">獄方名冊 // BLOCK 02</t>
+          <t xml:space="preserve">慣犯榜 — 入監次數 TOP 10</t>
         </is>
       </c>
       <c r="E114"/>
@@ -2708,17 +2708,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">348</t>
+          <t xml:space="preserve">384</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員·標題</t>
+          <t xml:space="preserve">名人堂·榜二</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員</t>
+          <t xml:space="preserve">人氣榜 — 收到探監 TOP 10</t>
         </is>
       </c>
       <c r="E115"/>
@@ -2731,17 +2731,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">349</t>
+          <t xml:space="preserve">391</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員·說明</t>
+          <t xml:space="preserve">名人堂·空狀態</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">看守這座監獄、確保沒人逃稿的人。</t>
+          <t xml:space="preserve">名冊整備中…</t>
         </is>
       </c>
       <c r="E116"/>
@@ -2754,17 +2754,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">351</t>
+          <t xml:space="preserve">399</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員·空狀態</t>
+          <t xml:space="preserve">名人堂·隱名</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">名冊整備中…</t>
+          <t xml:space="preserve">〔機密犯人〕</t>
         </is>
       </c>
       <c r="E117"/>
@@ -2777,17 +2777,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">359</t>
+          <t xml:space="preserve">400</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">自介 fallback(人員/犯人)</t>
+          <t xml:space="preserve">名人堂·第一名徽章</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">〔機密資料未公開〕</t>
+          <t xml:space="preserve">重刑犯</t>
         </is>
       </c>
       <c r="E118"/>
@@ -2800,17 +2800,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">370</t>
+          <t xml:space="preserve">402</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆·eyebrow</t>
+          <t xml:space="preserve">名人堂·次數後綴</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑紀錄 // BLOCK 03</t>
+          <t xml:space="preserve">〈數字〉 次</t>
         </is>
       </c>
       <c r="E119"/>
@@ -2823,17 +2823,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">371</t>
+          <t xml:space="preserve">416</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆·標題</t>
+          <t xml:space="preserve">收費價目·eyebrow</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆</t>
+          <t xml:space="preserve">營業項目 // BLOCK 05</t>
         </is>
       </c>
       <c r="E120"/>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">372</t>
+          <t xml:space="preserve">417</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆·說明</t>
+          <t xml:space="preserve">收費價目·標題</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">自願把服刑紀錄公開示眾的犯人。沒被趕完的稿，大家一起看著。</t>
+          <t xml:space="preserve">收費價目</t>
         </is>
       </c>
       <c r="E121"/>
@@ -2869,17 +2869,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">374</t>
+          <t xml:space="preserve">418</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆·載入中</t>
+          <t xml:space="preserve">收費價目·說明</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">調閱服刑紀錄中…</t>
+          <t xml:space="preserve">把自己關起來也要明碼標價。保釋金制度為增加體驗之設計，非強制消費；所有互動皆為角色扮演，請保持良好的 RP 禮儀。</t>
         </is>
       </c>
       <c r="E122"/>
@@ -2892,17 +2892,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">375</t>
+          <t xml:space="preserve">436</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆·空狀態</t>
+          <t xml:space="preserve">收費價目·保釋金標題</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">目前無人願意公開服刑紀錄</t>
+          <t xml:space="preserve">保釋金退還規則</t>
         </is>
       </c>
       <c r="E123"/>
@@ -2915,17 +2915,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">395</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·eyebrow</t>
+          <t xml:space="preserve">收費價目·加購標題</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄名人堂 // BLOCK 04</t>
+          <t xml:space="preserve">加購項目 // ADD-ON</t>
         </is>
       </c>
       <c r="E124"/>
@@ -2938,17 +2938,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">396</t>
+          <t xml:space="preserve">465</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·標題</t>
+          <t xml:space="preserve">趕稿場次·eyebrow</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂</t>
+          <t xml:space="preserve">服刑梯次 // BLOCK 06</t>
         </is>
       </c>
       <c r="E125"/>
@@ -2961,17 +2961,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">397</t>
+          <t xml:space="preserve">466</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·說明</t>
+          <t xml:space="preserve">趕稿場次·標題</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑最勤、人氣最高的犯人。次數照實計入，名字是否公開由本人決定。</t>
+          <t xml:space="preserve">近期趕稿場次</t>
         </is>
       </c>
       <c r="E126"/>
@@ -2984,17 +2984,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t xml:space="preserve">467</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·榜一</t>
+          <t xml:space="preserve">趕稿場次·說明</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">慣犯榜 — 入監次數 TOP 10</t>
+          <t xml:space="preserve">選一個梯次自首入監。額滿停止收監，過期梯次已結案。</t>
         </is>
       </c>
       <c r="E127"/>
@@ -3007,17 +3007,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">401</t>
+          <t xml:space="preserve">469</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·榜二</t>
+          <t xml:space="preserve">趕稿場次·載入中</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">人氣榜 — 收到探監 TOP 10</t>
+          <t xml:space="preserve">調閱梯次中…</t>
         </is>
       </c>
       <c r="E128"/>
@@ -3030,17 +3030,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">408</t>
+          <t xml:space="preserve">470</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·空狀態</t>
+          <t xml:space="preserve">趕稿場次·空狀態</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">名冊整備中…</t>
+          <t xml:space="preserve">目前沒有開放收監的梯次</t>
         </is>
       </c>
       <c r="E129"/>
@@ -3053,17 +3053,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">416</t>
+          <t xml:space="preserve">478</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·隱名</t>
+          <t xml:space="preserve">趕稿場次·人數</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">〔機密犯人〕</t>
+          <t xml:space="preserve">已報名 〈X〉 / 〈Y〉 / 已報名 〈X〉 人</t>
         </is>
       </c>
       <c r="E130"/>
@@ -3076,17 +3076,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">417</t>
+          <t xml:space="preserve">491</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·第一名徽章</t>
+          <t xml:space="preserve">趕稿場次·入監按鈕</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">重刑犯</t>
+          <t xml:space="preserve">入監服刑</t>
         </is>
       </c>
       <c r="E131"/>
@@ -3099,17 +3099,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">493</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·次數後綴</t>
+          <t xml:space="preserve">趕稿場次·按鈕(額滿/狀態)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">〈數字〉 次</t>
+          <t xml:space="preserve">已額滿 / 〈狀態〉</t>
         </is>
       </c>
       <c r="E132"/>
@@ -3122,17 +3122,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">433</t>
+          <t xml:space="preserve">503</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·eyebrow</t>
+          <t xml:space="preserve">頁尾·品牌</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">營業項目 // BLOCK 05</t>
+          <t xml:space="preserve">死線監獄</t>
         </is>
       </c>
       <c r="E133"/>
@@ -3145,17 +3145,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">504</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·標題</t>
+          <t xml:space="preserve">頁尾·副標</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目</t>
+          <t xml:space="preserve">DEADLINE PRISON · 趕稿收容所 · since 2026</t>
         </is>
       </c>
       <c r="E134"/>
@@ -3168,17 +3168,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">435</t>
+          <t xml:space="preserve">505</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·說明</t>
+          <t xml:space="preserve">頁尾·地址</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">把自己關起來也要明碼標價。保釋金制度為增加體驗之設計，非強制消費；所有互動皆為角色扮演，請保持良好的 RP 禮儀。</t>
+          <t xml:space="preserve">服刑地點：巴哈姆特 - 薰衣草苗園 - 1區 - 18號</t>
         </is>
       </c>
       <c r="E135"/>
@@ -3191,17 +3191,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">453</t>
+          <t xml:space="preserve">506</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·保釋金標題</t>
+          <t xml:space="preserve">頁尾·結案章</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">保釋金退還規則</t>
+          <t xml:space="preserve">結案 · CLASSIFIED</t>
         </is>
       </c>
       <c r="E136"/>
@@ -3214,17 +3214,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">466</t>
+          <t xml:space="preserve">515</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·加購標題</t>
+          <t xml:space="preserve">Modal·關閉</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">加購項目 // ADD-ON</t>
+          <t xml:space="preserve">✕</t>
         </is>
       </c>
       <c r="E137"/>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">482</t>
+          <t xml:space="preserve">517</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·eyebrow</t>
+          <t xml:space="preserve">Modal·eyebrow</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑梯次 // BLOCK 06</t>
+          <t xml:space="preserve">入監服刑 · INTAKE</t>
         </is>
       </c>
       <c r="E138"/>
@@ -3260,17 +3260,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">483</t>
+          <t xml:space="preserve">519</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·標題</t>
+          <t xml:space="preserve">Modal·欄位</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">近期趕稿場次</t>
+          <t xml:space="preserve">梯次編號</t>
         </is>
       </c>
       <c r="E139"/>
@@ -3283,17 +3283,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">484</t>
+          <t xml:space="preserve">520</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·說明</t>
+          <t xml:space="preserve">Modal·欄位(日期未定)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">選一個梯次自首入監。額滿停止收監，過期梯次已結案。</t>
+          <t xml:space="preserve">服刑日期 /(未定)</t>
         </is>
       </c>
       <c r="E140"/>
@@ -3306,17 +3306,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">486</t>
+          <t xml:space="preserve">521</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·載入中</t>
+          <t xml:space="preserve">Modal·欄位(不限)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">調閱梯次中…</t>
+          <t xml:space="preserve">收容情況 / 〈X〉 ／ 不限</t>
         </is>
       </c>
       <c r="E141"/>
@@ -3329,17 +3329,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">487</t>
+          <t xml:space="preserve">527</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·空狀態</t>
+          <t xml:space="preserve">Modal·未登入說明</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">目前沒有開放收監的梯次</t>
+          <t xml:space="preserve">入監採 Discord 登入，登入後自動帶入你的 DC 身分作為服刑名冊紀錄，無需另填聯絡方式。</t>
         </is>
       </c>
       <c r="E142"/>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">495</t>
+          <t xml:space="preserve">528</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·人數</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">已報名 〈X〉 / 〈Y〉 / 已報名 〈X〉 人</t>
+          <t xml:space="preserve">以 Discord 登入入監</t>
         </is>
       </c>
       <c r="E143"/>
@@ -3375,17 +3375,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">508</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·入監按鈕</t>
+          <t xml:space="preserve">Modal·已報名說明</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監服刑</t>
+          <t xml:space="preserve">你已在此梯次服刑名冊上。</t>
         </is>
       </c>
       <c r="E144"/>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">510</t>
+          <t xml:space="preserve">533</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·按鈕(額滿/狀態)</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">已額滿 / 〈狀態〉</t>
+          <t xml:space="preserve">取消預約</t>
         </is>
       </c>
       <c r="E145"/>
@@ -3421,17 +3421,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">520</t>
+          <t xml:space="preserve">537</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·品牌</t>
+          <t xml:space="preserve">Modal·已取消說明</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">死線監獄</t>
+          <t xml:space="preserve">你先前已取消此梯次。要重新登記入監名冊嗎？</t>
         </is>
       </c>
       <c r="E146"/>
@@ -3444,17 +3444,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">538</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·副標</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEADLINE PRISON · 趕稿收容所 · since 2026</t>
+          <t xml:space="preserve">處理中… / 重新報名</t>
         </is>
       </c>
       <c r="E147"/>
@@ -3467,17 +3467,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">522</t>
+          <t xml:space="preserve">545</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·地址</t>
+          <t xml:space="preserve">Modal·沿用身分說明</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑地點：巴哈姆特 - 薰衣草苗園 - 1區 - 18號</t>
+          <t xml:space="preserve">以 〈暱稱〉 身分入監，確認後登入服刑名冊。</t>
         </is>
       </c>
       <c r="E148"/>
@@ -3490,17 +3490,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">523</t>
+          <t xml:space="preserve">547</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·結案章</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">結案 · CLASSIFIED</t>
+          <t xml:space="preserve">收監中… / 確認入監</t>
         </is>
       </c>
       <c r="E149"/>
@@ -3513,17 +3513,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">552</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·關閉</t>
+          <t xml:space="preserve">Modal·補填說明</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">✕</t>
+          <t xml:space="preserve">入監前請設定你的服刑暱稱與頭像（將作為本梯次名冊的顯示資料）。</t>
         </is>
       </c>
       <c r="E150"/>
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">534</t>
+          <t xml:space="preserve">554</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·eyebrow</t>
+          <t xml:space="preserve">Modal·欄位</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監服刑 · INTAKE</t>
+          <t xml:space="preserve">服刑暱稱（必填）</t>
         </is>
       </c>
       <c r="E151"/>
@@ -3559,17 +3559,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">536</t>
+          <t xml:space="preserve">555</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位</t>
+          <t xml:space="preserve">Modal·placeholder</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">梯次編號</t>
+          <t xml:space="preserve">顯示在名冊上的暱稱</t>
         </is>
       </c>
       <c r="E152"/>
@@ -3582,17 +3582,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">537</t>
+          <t xml:space="preserve">558</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位(日期未定)</t>
+          <t xml:space="preserve">Modal·欄位</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑日期 /(未定)</t>
+          <t xml:space="preserve">頭像</t>
         </is>
       </c>
       <c r="E153"/>
@@ -3605,17 +3605,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">538</t>
+          <t xml:space="preserve">562</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位(不限)</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">收容情況 / 〈X〉 ／ 不限</t>
+          <t xml:space="preserve">收監中… / 確認入監</t>
         </is>
       </c>
       <c r="E154"/>
@@ -3623,324 +3623,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+          <t xml:space="preserve">index.html</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">544</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·未登入說明</t>
+          <t xml:space="preserve">瀏覽器分頁標題</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監採 Discord 登入，登入後自動帶入你的 DC 身分作為服刑名冊紀錄，無需另填聯絡方式。</t>
+          <t xml:space="preserve">死線監獄 ｜ DEADLINE PRISON</t>
         </is>
       </c>
       <c r="E155"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">545</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·按鈕</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">以 Discord 登入入監</t>
-        </is>
-      </c>
-      <c r="E156"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">549</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·已報名說明</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">你已在此梯次服刑名冊上。</t>
-        </is>
-      </c>
-      <c r="E157"/>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">550</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·按鈕</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">取消預約</t>
-        </is>
-      </c>
-      <c r="E158"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">554</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·已取消說明</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">你先前已取消此梯次。要重新登記入監名冊嗎？</t>
-        </is>
-      </c>
-      <c r="E159"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">555</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·按鈕</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">處理中… / 重新報名</t>
-        </is>
-      </c>
-      <c r="E160"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">562</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·沿用身分說明</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">以 〈暱稱〉 身分入監，確認後登入服刑名冊。</t>
-        </is>
-      </c>
-      <c r="E161"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">564</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·按鈕</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">收監中… / 確認入監</t>
-        </is>
-      </c>
-      <c r="E162"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">569</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·補填說明</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">入監前請設定你的服刑暱稱與頭像（將作為本梯次名冊的顯示資料）。</t>
-        </is>
-      </c>
-      <c r="E163"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">571</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·欄位</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">服刑暱稱（必填）</t>
-        </is>
-      </c>
-      <c r="E164"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">572</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·placeholder</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">顯示在名冊上的暱稱</t>
-        </is>
-      </c>
-      <c r="E165"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">575</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·欄位</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">頭像</t>
-        </is>
-      </c>
-      <c r="E166"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">579</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modal·按鈕</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">收監中… / 確認入監</t>
-        </is>
-      </c>
-      <c r="E167"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">index.html</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">瀏覽器分頁標題</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">死線監獄 ｜ DEADLINE PRISON</t>
-        </is>
-      </c>
-      <c r="E168"/>
     </row>
   </sheetData>
 </worksheet>

--- a/文案總表.xlsx
+++ b/文案總表.xlsx
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">116</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">117</t>
+          <t xml:space="preserve">121</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·收監成功</t>
+          <t xml:space="preserve">系統訊息·密鑰核對失敗</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">收監成功。鈴響時見。</t>
+          <t xml:space="preserve">密鑰核對失敗，請稍後再試。</t>
         </is>
       </c>
       <c r="E58"/>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·已報名</t>
+          <t xml:space="preserve">系統訊息·密鑰不正確</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">你已在此梯次服刑名冊上。</t>
+          <t xml:space="preserve">密鑰不正確，請確認後重試。</t>
         </is>
       </c>
       <c r="E59"/>
@@ -1443,17 +1443,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">218</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·已停收監</t>
+          <t xml:space="preserve">系統訊息·收監成功</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">此梯次已停止收監。</t>
+          <t xml:space="preserve">收監成功。鈴響時見。</t>
         </is>
       </c>
       <c r="E60"/>
@@ -1466,17 +1466,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">202</t>
+          <t xml:space="preserve">219</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·未登入</t>
+          <t xml:space="preserve">系統訊息·已報名</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">請先以 Discord 登入。</t>
+          <t xml:space="preserve">你已在此梯次服刑名冊上。</t>
         </is>
       </c>
       <c r="E61"/>
@@ -1489,17 +1489,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">203</t>
+          <t xml:space="preserve">220</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·收監失敗</t>
+          <t xml:space="preserve">系統訊息·已停收監</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">收監失敗，請稍後再試。</t>
+          <t xml:space="preserve">此梯次已停止收監。</t>
         </is>
       </c>
       <c r="E62"/>
@@ -1512,17 +1512,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">212</t>
+          <t xml:space="preserve">221</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·取消確認</t>
+          <t xml:space="preserve">系統訊息·密鑰錯誤(送出)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">確定取消本梯次預約？</t>
+          <t xml:space="preserve">通行密鑰不正確，請重新開啟報名並輸入密鑰。</t>
         </is>
       </c>
       <c r="E63"/>
@@ -1535,17 +1535,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">216</t>
+          <t xml:space="preserve">222</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·已取消/取消失敗</t>
+          <t xml:space="preserve">系統訊息·未登入</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">已取消預約。 / 取消失敗，請稍後再試。</t>
+          <t xml:space="preserve">請先以 Discord 登入。</t>
         </is>
       </c>
       <c r="E64"/>
@@ -1558,17 +1558,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·已停收監</t>
+          <t xml:space="preserve">系統訊息·收監失敗</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">此梯次已停止收監。</t>
+          <t xml:space="preserve">收監失敗，請稍後再試。</t>
         </is>
       </c>
       <c r="E65"/>
@@ -1581,17 +1581,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">226</t>
+          <t xml:space="preserve">232</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">系統訊息·重新報名失敗/成功</t>
+          <t xml:space="preserve">系統訊息·取消確認</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">重新報名失敗，請稍後再試。 / 已重新登記入監名冊。</t>
+          <t xml:space="preserve">確定取消本梯次預約？</t>
         </is>
       </c>
       <c r="E66"/>
@@ -1604,17 +1604,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">238</t>
+          <t xml:space="preserve">236</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·品牌</t>
+          <t xml:space="preserve">系統訊息·已取消/取消失敗</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">死線監獄</t>
+          <t xml:space="preserve">已取消預約。 / 取消失敗，請稍後再試。</t>
         </is>
       </c>
       <c r="E67"/>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">242</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·選單</t>
+          <t xml:space="preserve">系統訊息·已停收監</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知</t>
+          <t xml:space="preserve">此梯次已停止收監。</t>
         </is>
       </c>
       <c r="E68"/>
@@ -1650,17 +1650,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">241</t>
+          <t xml:space="preserve">246</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·選單</t>
+          <t xml:space="preserve">系統訊息·重新報名失敗/成功</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員</t>
+          <t xml:space="preserve">重新報名失敗，請稍後再試。 / 已重新登記入監名冊。</t>
         </is>
       </c>
       <c r="E69"/>
@@ -1673,17 +1673,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">242</t>
+          <t xml:space="preserve">258</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·選單</t>
+          <t xml:space="preserve">導覽·品牌</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆</t>
+          <t xml:space="preserve">死線監獄</t>
         </is>
       </c>
       <c r="E70"/>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">243</t>
+          <t xml:space="preserve">260</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂</t>
+          <t xml:space="preserve">服刑須知</t>
         </is>
       </c>
       <c r="E71"/>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">244</t>
+          <t xml:space="preserve">261</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目</t>
+          <t xml:space="preserve">監獄人員</t>
         </is>
       </c>
       <c r="E72"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">245</t>
+          <t xml:space="preserve">262</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次</t>
+          <t xml:space="preserve">犯人牆</t>
         </is>
       </c>
       <c r="E73"/>
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">248</t>
+          <t xml:space="preserve">263</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·系統入口</t>
+          <t xml:space="preserve">導覽·選單</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACCESS · 監獄系統</t>
+          <t xml:space="preserve">名人堂</t>
         </is>
       </c>
       <c r="E74"/>
@@ -1788,17 +1788,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">249</t>
+          <t xml:space="preserve">264</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">導覽·Discord aria</t>
+          <t xml:space="preserve">導覽·選單</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discord</t>
+          <t xml:space="preserve">收費價目</t>
         </is>
       </c>
       <c r="E75"/>
@@ -1811,17 +1811,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">258</t>
+          <t xml:space="preserve">265</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">漢堡·aria</t>
+          <t xml:space="preserve">導覽·選單</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">選單</t>
+          <t xml:space="preserve">趕稿場次</t>
         </is>
       </c>
       <c r="E76"/>
@@ -1834,17 +1834,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">273</t>
+          <t xml:space="preserve">268</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">抽屜選單</t>
+          <t xml:space="preserve">導覽·系統入口</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知</t>
+          <t xml:space="preserve">ACCESS · 監獄系統</t>
         </is>
       </c>
       <c r="E77"/>
@@ -1857,17 +1857,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">273</t>
+          <t xml:space="preserve">269</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">抽屜選單</t>
+          <t xml:space="preserve">導覽·Discord aria</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員</t>
+          <t xml:space="preserve">Discord</t>
         </is>
       </c>
       <c r="E78"/>
@@ -1880,17 +1880,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">273</t>
+          <t xml:space="preserve">278</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">抽屜選單</t>
+          <t xml:space="preserve">漢堡·aria</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆</t>
+          <t xml:space="preserve">選單</t>
         </is>
       </c>
       <c r="E79"/>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">274</t>
+          <t xml:space="preserve">293</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂</t>
+          <t xml:space="preserve">服刑須知</t>
         </is>
       </c>
       <c r="E80"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">274</t>
+          <t xml:space="preserve">293</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目</t>
+          <t xml:space="preserve">監獄人員</t>
         </is>
       </c>
       <c r="E81"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">274</t>
+          <t xml:space="preserve">293</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次</t>
+          <t xml:space="preserve">犯人牆</t>
         </is>
       </c>
       <c r="E82"/>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">284</t>
+          <t xml:space="preserve">294</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·收容徽章</t>
+          <t xml:space="preserve">抽屜選單</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">收容中 · INTAKE OPEN · 24H</t>
+          <t xml:space="preserve">名人堂</t>
         </is>
       </c>
       <c r="E83"/>
@@ -1995,17 +1995,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">285</t>
+          <t xml:space="preserve">294</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·主標</t>
+          <t xml:space="preserve">抽屜選單</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">死線監獄</t>
+          <t xml:space="preserve">收費價目</t>
         </is>
       </c>
       <c r="E84"/>
@@ -2018,17 +2018,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">286</t>
+          <t xml:space="preserve">294</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·編號條</t>
+          <t xml:space="preserve">抽屜選單</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEADLINE PRISON · NO.0118</t>
+          <t xml:space="preserve">趕稿場次</t>
         </is>
       </c>
       <c r="E85"/>
@@ -2041,17 +2041,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">287</t>
+          <t xml:space="preserve">304</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·標語</t>
+          <t xml:space="preserve">Hero·收容徽章</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">把自己關進來，服完這一頁死線。沒有逃獄，只有交稿。</t>
+          <t xml:space="preserve">收容中 · INTAKE OPEN · 24H</t>
         </is>
       </c>
       <c r="E86"/>
@@ -2064,17 +2064,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">288</t>
+          <t xml:space="preserve">305</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·拘留登記 aria</t>
+          <t xml:space="preserve">Hero·主標</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">拘留登記</t>
+          <t xml:space="preserve">死線監獄</t>
         </is>
       </c>
       <c r="E87"/>
@@ -2087,17 +2087,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">289</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·拘留卡</t>
+          <t xml:space="preserve">Hero·編號條</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">罪名／慣性拖稿</t>
+          <t xml:space="preserve">DEADLINE PRISON · NO.0118</t>
         </is>
       </c>
       <c r="E88"/>
@@ -2110,17 +2110,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">290</t>
+          <t xml:space="preserve">307</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·拘留卡</t>
+          <t xml:space="preserve">Hero·標語</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">刑期／一個番茄鐘起</t>
+          <t xml:space="preserve">把自己關進來，服完這一頁死線。沒有逃獄，只有交稿。</t>
         </is>
       </c>
       <c r="E89"/>
@@ -2133,17 +2133,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">308</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·拘留卡</t>
+          <t xml:space="preserve">Hero·拘留登記 aria</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">保釋／不受理</t>
+          <t xml:space="preserve">拘留登記</t>
         </is>
       </c>
       <c r="E90"/>
@@ -2156,17 +2156,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">294</t>
+          <t xml:space="preserve">309</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·主CTA</t>
+          <t xml:space="preserve">Hero·拘留卡</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監服刑 ▸</t>
+          <t xml:space="preserve">罪名／慣性拖稿</t>
         </is>
       </c>
       <c r="E91"/>
@@ -2179,17 +2179,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">296</t>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero·滾動提示</t>
+          <t xml:space="preserve">Hero·拘留卡</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">▼ 向下了解服刑流程</t>
+          <t xml:space="preserve">刑期／一個番茄鐘起</t>
         </is>
       </c>
       <c r="E92"/>
@@ -2202,17 +2202,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">303</t>
+          <t xml:space="preserve">311</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·eyebrow</t>
+          <t xml:space="preserve">Hero·拘留卡</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知 // BLOCK 01</t>
+          <t xml:space="preserve">保釋／不受理</t>
         </is>
       </c>
       <c r="E93"/>
@@ -2225,17 +2225,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">304</t>
+          <t xml:space="preserve">314</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·標題</t>
+          <t xml:space="preserve">Hero·主CTA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">這裡關的，是趕不完稿的人</t>
+          <t xml:space="preserve">入監服刑 ▸</t>
         </is>
       </c>
       <c r="E94"/>
@@ -2248,17 +2248,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">305</t>
+          <t xml:space="preserve">316</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·說明</t>
+          <t xml:space="preserve">Hero·滾動提示</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">死線監獄是一間以「番茄鐘」執行的趕稿收容所。入監即上鎖，鈴響才放風，全程同步直播犯人服刑進度——你不是一個人在趕，是一群人一起服刑。</t>
+          <t xml:space="preserve">▼ 向下了解服刑流程</t>
         </is>
       </c>
       <c r="E95"/>
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">323</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·地點</t>
+          <t xml:space="preserve">服刑須知·eyebrow</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑地點：巴哈姆特 - 薰衣草苗園 - 1區 - 18號</t>
+          <t xml:space="preserve">服刑須知 // BLOCK 01</t>
         </is>
       </c>
       <c r="E96"/>
@@ -2294,17 +2294,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">313</t>
+          <t xml:space="preserve">324</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·節奏標題</t>
+          <t xml:space="preserve">服刑須知·標題</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑節奏 · POMODORO CYCLE</t>
+          <t xml:space="preserve">這裡關的，是趕不完稿的人</t>
         </is>
       </c>
       <c r="E97"/>
@@ -2317,17 +2317,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">319</t>
+          <t xml:space="preserve">325</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·圖例</t>
+          <t xml:space="preserve">服刑須知·說明</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">專注 25 分</t>
+          <t xml:space="preserve">死線監獄是一間以「番茄鐘」執行的趕稿收容所。入監即上鎖，鈴響才放風，全程同步直播犯人服刑進度——你不是一個人在趕，是一群人一起服刑。</t>
         </is>
       </c>
       <c r="E98"/>
@@ -2340,17 +2340,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">320</t>
+          <t xml:space="preserve">326</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·圖例</t>
+          <t xml:space="preserve">服刑須知·地點</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">放風 5 分</t>
+          <t xml:space="preserve">服刑地點：巴哈姆特 - 薰衣草苗園 - 1區 - 18號</t>
         </is>
       </c>
       <c r="E99"/>
@@ -2363,17 +2363,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑須知·圖例</t>
+          <t xml:space="preserve">服刑須知·節奏標題</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">長休 15 分（每 4 輪）</t>
+          <t xml:space="preserve">服刑節奏 · POMODORO CYCLE</t>
         </is>
       </c>
       <c r="E100"/>
@@ -2386,17 +2386,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">330</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員·eyebrow</t>
+          <t xml:space="preserve">服刑須知·圖例</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">獄方名冊 // BLOCK 02</t>
+          <t xml:space="preserve">專注 25 分</t>
         </is>
       </c>
       <c r="E101"/>
@@ -2409,17 +2409,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">340</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員·標題</t>
+          <t xml:space="preserve">服刑須知·圖例</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員</t>
+          <t xml:space="preserve">放風 5 分</t>
         </is>
       </c>
       <c r="E102"/>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員·說明</t>
+          <t xml:space="preserve">服刑須知·圖例</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">看守這座監獄、確保沒人逃稿的人。</t>
+          <t xml:space="preserve">長休 15 分（每 4 輪）</t>
         </is>
       </c>
       <c r="E103"/>
@@ -2455,17 +2455,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">334</t>
+          <t xml:space="preserve">350</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄人員·空狀態</t>
+          <t xml:space="preserve">監獄人員·eyebrow</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">名冊整備中…</t>
+          <t xml:space="preserve">獄方名冊 // BLOCK 02</t>
         </is>
       </c>
       <c r="E104"/>
@@ -2478,17 +2478,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">351</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">自介 fallback(人員/犯人)</t>
+          <t xml:space="preserve">監獄人員·標題</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">〔機密資料未公開〕</t>
+          <t xml:space="preserve">監獄人員</t>
         </is>
       </c>
       <c r="E105"/>
@@ -2501,17 +2501,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">353</t>
+          <t xml:space="preserve">352</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆·eyebrow</t>
+          <t xml:space="preserve">監獄人員·說明</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑紀錄 // BLOCK 03</t>
+          <t xml:space="preserve">看守這座監獄、確保沒人逃稿的人。</t>
         </is>
       </c>
       <c r="E106"/>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆·標題</t>
+          <t xml:space="preserve">監獄人員·空狀態</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆</t>
+          <t xml:space="preserve">名冊整備中…</t>
         </is>
       </c>
       <c r="E107"/>
@@ -2547,17 +2547,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">355</t>
+          <t xml:space="preserve">362</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆·說明</t>
+          <t xml:space="preserve">自介 fallback(人員/犯人)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">自願把服刑紀錄公開示眾的犯人。沒被趕完的稿，大家一起看著。</t>
+          <t xml:space="preserve">〔機密資料未公開〕</t>
         </is>
       </c>
       <c r="E108"/>
@@ -2570,17 +2570,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">357</t>
+          <t xml:space="preserve">373</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆·載入中</t>
+          <t xml:space="preserve">犯人牆·eyebrow</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">調閱服刑紀錄中…</t>
+          <t xml:space="preserve">服刑紀錄 // BLOCK 03</t>
         </is>
       </c>
       <c r="E109"/>
@@ -2593,17 +2593,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">358</t>
+          <t xml:space="preserve">374</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人牆·空狀態</t>
+          <t xml:space="preserve">犯人牆·標題</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">目前無人願意公開服刑紀錄</t>
+          <t xml:space="preserve">犯人牆</t>
         </is>
       </c>
       <c r="E110"/>
@@ -2616,17 +2616,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">378</t>
+          <t xml:space="preserve">375</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·eyebrow</t>
+          <t xml:space="preserve">犯人牆·說明</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄名人堂 // BLOCK 04</t>
+          <t xml:space="preserve">自願把服刑紀錄公開示眾的犯人。沒被趕完的稿，大家一起看著。</t>
         </is>
       </c>
       <c r="E111"/>
@@ -2639,17 +2639,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">379</t>
+          <t xml:space="preserve">377</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·標題</t>
+          <t xml:space="preserve">犯人牆·載入中</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂</t>
+          <t xml:space="preserve">調閱服刑紀錄中…</t>
         </is>
       </c>
       <c r="E112"/>
@@ -2662,17 +2662,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">380</t>
+          <t xml:space="preserve">378</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·說明</t>
+          <t xml:space="preserve">犯人牆·空狀態</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑最勤、人氣最高的犯人。次數照實計入，名字是否公開由本人決定。</t>
+          <t xml:space="preserve">目前無人願意公開服刑紀錄</t>
         </is>
       </c>
       <c r="E113"/>
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">383</t>
+          <t xml:space="preserve">398</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·榜一</t>
+          <t xml:space="preserve">名人堂·eyebrow</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">慣犯榜 — 入監次數 TOP 10</t>
+          <t xml:space="preserve">監獄名人堂 // BLOCK 04</t>
         </is>
       </c>
       <c r="E114"/>
@@ -2708,17 +2708,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">384</t>
+          <t xml:space="preserve">399</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·榜二</t>
+          <t xml:space="preserve">名人堂·標題</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">人氣榜 — 收到探監 TOP 10</t>
+          <t xml:space="preserve">名人堂</t>
         </is>
       </c>
       <c r="E115"/>
@@ -2731,17 +2731,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">391</t>
+          <t xml:space="preserve">400</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·空狀態</t>
+          <t xml:space="preserve">名人堂·說明</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">名冊整備中…</t>
+          <t xml:space="preserve">服刑最勤、人氣最高的犯人。次數照實計入，名字是否公開由本人決定。</t>
         </is>
       </c>
       <c r="E116"/>
@@ -2754,17 +2754,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">399</t>
+          <t xml:space="preserve">403</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·隱名</t>
+          <t xml:space="preserve">名人堂·榜一</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">〔機密犯人〕</t>
+          <t xml:space="preserve">慣犯榜 — 入監次數 TOP 10</t>
         </is>
       </c>
       <c r="E117"/>
@@ -2777,17 +2777,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t xml:space="preserve">404</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·第一名徽章</t>
+          <t xml:space="preserve">名人堂·榜二</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">重刑犯</t>
+          <t xml:space="preserve">人氣榜 — 收到探監 TOP 10</t>
         </is>
       </c>
       <c r="E118"/>
@@ -2800,17 +2800,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">402</t>
+          <t xml:space="preserve">411</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·次數後綴</t>
+          <t xml:space="preserve">名人堂·空狀態</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">〈數字〉 次</t>
+          <t xml:space="preserve">名冊整備中…</t>
         </is>
       </c>
       <c r="E119"/>
@@ -2823,17 +2823,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">416</t>
+          <t xml:space="preserve">419</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·eyebrow</t>
+          <t xml:space="preserve">名人堂·隱名</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">營業項目 // BLOCK 05</t>
+          <t xml:space="preserve">〔機密犯人〕</t>
         </is>
       </c>
       <c r="E120"/>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">417</t>
+          <t xml:space="preserve">420</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·標題</t>
+          <t xml:space="preserve">名人堂·第一名徽章</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目</t>
+          <t xml:space="preserve">重刑犯</t>
         </is>
       </c>
       <c r="E121"/>
@@ -2869,17 +2869,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">418</t>
+          <t xml:space="preserve">422</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·說明</t>
+          <t xml:space="preserve">名人堂·次數後綴</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">把自己關起來也要明碼標價。保釋金制度為增加體驗之設計，非強制消費；所有互動皆為角色扮演，請保持良好的 RP 禮儀。</t>
+          <t xml:space="preserve">〈數字〉 次</t>
         </is>
       </c>
       <c r="E122"/>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·保釋金標題</t>
+          <t xml:space="preserve">收費價目·eyebrow</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">保釋金退還規則</t>
+          <t xml:space="preserve">營業項目 // BLOCK 05</t>
         </is>
       </c>
       <c r="E123"/>
@@ -2915,17 +2915,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">437</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·加購標題</t>
+          <t xml:space="preserve">收費價目·標題</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">加購項目 // ADD-ON</t>
+          <t xml:space="preserve">收費價目</t>
         </is>
       </c>
       <c r="E124"/>
@@ -2938,17 +2938,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">465</t>
+          <t xml:space="preserve">438</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·eyebrow</t>
+          <t xml:space="preserve">收費價目·說明</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑梯次 // BLOCK 06</t>
+          <t xml:space="preserve">把自己關起來也要明碼標價。保釋金制度為增加體驗之設計，非強制消費；所有互動皆為角色扮演，請保持良好的 RP 禮儀。</t>
         </is>
       </c>
       <c r="E125"/>
@@ -2961,17 +2961,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">466</t>
+          <t xml:space="preserve">456</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·標題</t>
+          <t xml:space="preserve">收費價目·保釋金標題</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">近期趕稿場次</t>
+          <t xml:space="preserve">保釋金退還規則</t>
         </is>
       </c>
       <c r="E126"/>
@@ -2984,17 +2984,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">467</t>
+          <t xml:space="preserve">469</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·說明</t>
+          <t xml:space="preserve">收費價目·加購標題</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">選一個梯次自首入監。額滿停止收監，過期梯次已結案。</t>
+          <t xml:space="preserve">加購項目 // ADD-ON</t>
         </is>
       </c>
       <c r="E127"/>
@@ -3007,17 +3007,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">469</t>
+          <t xml:space="preserve">485</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·載入中</t>
+          <t xml:space="preserve">趕稿場次·eyebrow</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">調閱梯次中…</t>
+          <t xml:space="preserve">服刑梯次 // BLOCK 06</t>
         </is>
       </c>
       <c r="E128"/>
@@ -3030,17 +3030,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">470</t>
+          <t xml:space="preserve">486</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·空狀態</t>
+          <t xml:space="preserve">趕稿場次·標題</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">目前沒有開放收監的梯次</t>
+          <t xml:space="preserve">近期趕稿場次</t>
         </is>
       </c>
       <c r="E129"/>
@@ -3053,17 +3053,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">478</t>
+          <t xml:space="preserve">487</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·人數</t>
+          <t xml:space="preserve">趕稿場次·說明</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">已報名 〈X〉 / 〈Y〉 / 已報名 〈X〉 人</t>
+          <t xml:space="preserve">選一個梯次自首入監。額滿停止收監，過期梯次已結案。</t>
         </is>
       </c>
       <c r="E130"/>
@@ -3076,17 +3076,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">491</t>
+          <t xml:space="preserve">489</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·入監按鈕</t>
+          <t xml:space="preserve">趕稿場次·載入中</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監服刑</t>
+          <t xml:space="preserve">調閱梯次中…</t>
         </is>
       </c>
       <c r="E131"/>
@@ -3099,17 +3099,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">493</t>
+          <t xml:space="preserve">490</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·按鈕(額滿/狀態)</t>
+          <t xml:space="preserve">趕稿場次·空狀態</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">已額滿 / 〈狀態〉</t>
+          <t xml:space="preserve">目前沒有開放收監的梯次</t>
         </is>
       </c>
       <c r="E132"/>
@@ -3122,17 +3122,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">503</t>
+          <t xml:space="preserve">498</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·品牌</t>
+          <t xml:space="preserve">趕稿場次·人數</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">死線監獄</t>
+          <t xml:space="preserve">已報名 〈X〉 / 〈Y〉 / 已報名 〈X〉 人</t>
         </is>
       </c>
       <c r="E133"/>
@@ -3145,17 +3145,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">504</t>
+          <t xml:space="preserve">512</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·副標</t>
+          <t xml:space="preserve">趕稿場次·入監按鈕</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEADLINE PRISON · 趕稿收容所 · since 2026</t>
+          <t xml:space="preserve">入監服刑 /(密鑰場)密鑰入獄</t>
         </is>
       </c>
       <c r="E134"/>
@@ -3168,17 +3168,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">505</t>
+          <t xml:space="preserve">514</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·地址</t>
+          <t xml:space="preserve">趕稿場次·按鈕(額滿/狀態)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑地點：巴哈姆特 - 薰衣草苗園 - 1區 - 18號</t>
+          <t xml:space="preserve">已額滿 / 〈狀態〉</t>
         </is>
       </c>
       <c r="E135"/>
@@ -3191,17 +3191,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">506</t>
+          <t xml:space="preserve">524</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·結案章</t>
+          <t xml:space="preserve">頁尾·品牌</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">結案 · CLASSIFIED</t>
+          <t xml:space="preserve">死線監獄</t>
         </is>
       </c>
       <c r="E136"/>
@@ -3214,17 +3214,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">515</t>
+          <t xml:space="preserve">525</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·關閉</t>
+          <t xml:space="preserve">頁尾·副標</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">✕</t>
+          <t xml:space="preserve">DEADLINE PRISON · 趕稿收容所 · since 2026</t>
         </is>
       </c>
       <c r="E137"/>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">517</t>
+          <t xml:space="preserve">526</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·eyebrow</t>
+          <t xml:space="preserve">頁尾·地址</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監服刑 · INTAKE</t>
+          <t xml:space="preserve">服刑地點：巴哈姆特 - 薰衣草苗園 - 1區 - 18號</t>
         </is>
       </c>
       <c r="E138"/>
@@ -3260,17 +3260,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">519</t>
+          <t xml:space="preserve">527</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位</t>
+          <t xml:space="preserve">頁尾·結案章</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">梯次編號</t>
+          <t xml:space="preserve">結案 · CLASSIFIED</t>
         </is>
       </c>
       <c r="E139"/>
@@ -3283,17 +3283,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">520</t>
+          <t xml:space="preserve">536</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位(日期未定)</t>
+          <t xml:space="preserve">Modal·關閉</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑日期 /(未定)</t>
+          <t xml:space="preserve">✕</t>
         </is>
       </c>
       <c r="E140"/>
@@ -3306,17 +3306,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">521</t>
+          <t xml:space="preserve">538</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位(不限)</t>
+          <t xml:space="preserve">Modal·eyebrow</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">收容情況 / 〈X〉 ／ 不限</t>
+          <t xml:space="preserve">入監服刑 · INTAKE /(密鑰場)密鑰入獄 · INTAKE</t>
         </is>
       </c>
       <c r="E141"/>
@@ -3329,17 +3329,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">527</t>
+          <t xml:space="preserve">540</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·未登入說明</t>
+          <t xml:space="preserve">Modal·欄位</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監採 Discord 登入，登入後自動帶入你的 DC 身分作為服刑名冊紀錄，無需另填聯絡方式。</t>
+          <t xml:space="preserve">梯次編號</t>
         </is>
       </c>
       <c r="E142"/>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">528</t>
+          <t xml:space="preserve">541</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·按鈕</t>
+          <t xml:space="preserve">Modal·欄位(日期未定)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">以 Discord 登入入監</t>
+          <t xml:space="preserve">服刑日期 /(未定)</t>
         </is>
       </c>
       <c r="E143"/>
@@ -3375,17 +3375,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">532</t>
+          <t xml:space="preserve">542</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·已報名說明</t>
+          <t xml:space="preserve">Modal·欄位(不限)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">你已在此梯次服刑名冊上。</t>
+          <t xml:space="preserve">收容情況 / 〈X〉 ／ 不限</t>
         </is>
       </c>
       <c r="E144"/>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">533</t>
+          <t xml:space="preserve">548</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·按鈕</t>
+          <t xml:space="preserve">Modal·未登入說明</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">取消預約</t>
+          <t xml:space="preserve">入監採 Discord 登入，登入後自動帶入你的 DC 身分作為服刑名冊紀錄，無需另填聯絡方式。</t>
         </is>
       </c>
       <c r="E145"/>
@@ -3421,17 +3421,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">537</t>
+          <t xml:space="preserve">549</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·已取消說明</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">你先前已取消此梯次。要重新登記入監名冊嗎？</t>
+          <t xml:space="preserve">以 Discord 登入入監</t>
         </is>
       </c>
       <c r="E146"/>
@@ -3444,17 +3444,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">538</t>
+          <t xml:space="preserve">553</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·按鈕</t>
+          <t xml:space="preserve">Modal·已報名說明</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">處理中… / 重新報名</t>
+          <t xml:space="preserve">你已在此梯次服刑名冊上。</t>
         </is>
       </c>
       <c r="E147"/>
@@ -3467,17 +3467,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">545</t>
+          <t xml:space="preserve">554</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·沿用身分說明</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">以 〈暱稱〉 身分入監，確認後登入服刑名冊。</t>
+          <t xml:space="preserve">取消預約</t>
         </is>
       </c>
       <c r="E148"/>
@@ -3490,17 +3490,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">547</t>
+          <t xml:space="preserve">559</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·按鈕</t>
+          <t xml:space="preserve">Modal·密鑰場說明</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">收監中… / 確認入監</t>
+          <t xml:space="preserve">本梯次為密鑰場，請輸入通行密鑰後繼續報名。</t>
         </is>
       </c>
       <c r="E149"/>
@@ -3513,17 +3513,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">552</t>
+          <t xml:space="preserve">561</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·補填說明</t>
+          <t xml:space="preserve">Modal·欄位</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監前請設定你的服刑暱稱與頭像（將作為本梯次名冊的顯示資料）。</t>
+          <t xml:space="preserve">通行密鑰</t>
         </is>
       </c>
       <c r="E150"/>
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">554</t>
+          <t xml:space="preserve">562</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位</t>
+          <t xml:space="preserve">Modal·placeholder</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑暱稱（必填）</t>
+          <t xml:space="preserve">輸入通行密鑰</t>
         </is>
       </c>
       <c r="E151"/>
@@ -3559,17 +3559,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">555</t>
+          <t xml:space="preserve">568</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·placeholder</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">顯示在名冊上的暱稱</t>
+          <t xml:space="preserve">核對中… / 核對密鑰</t>
         </is>
       </c>
       <c r="E152"/>
@@ -3582,17 +3582,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">558</t>
+          <t xml:space="preserve">573</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位</t>
+          <t xml:space="preserve">Modal·已取消說明</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">頭像</t>
+          <t xml:space="preserve">你先前已取消此梯次。要重新登記入監名冊嗎？</t>
         </is>
       </c>
       <c r="E153"/>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">562</t>
+          <t xml:space="preserve">574</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">收監中… / 確認入監</t>
+          <t xml:space="preserve">處理中… / 重新報名</t>
         </is>
       </c>
       <c r="E154"/>
@@ -3623,25 +3623,186 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">581</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·沿用身分說明</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以 〈暱稱〉 身分入監，確認後登入服刑名冊。</t>
+        </is>
+      </c>
+      <c r="E155"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">583</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·按鈕</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收監中… / 確認入監</t>
+        </is>
+      </c>
+      <c r="E156"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">588</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·補填說明</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入監前請設定你的服刑暱稱與頭像（將作為本梯次名冊的顯示資料）。</t>
+        </is>
+      </c>
+      <c r="E157"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">590</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·欄位</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">服刑暱稱（必填）</t>
+        </is>
+      </c>
+      <c r="E158"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">591</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·placeholder</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">顯示在名冊上的暱稱</t>
+        </is>
+      </c>
+      <c r="E159"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">594</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·欄位</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">頭像</t>
+        </is>
+      </c>
+      <c r="E160"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·按鈕</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收監中… / 確認入監</t>
+        </is>
+      </c>
+      <c r="E161"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
           <t xml:space="preserve">index.html</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B162" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t xml:space="preserve">瀏覽器分頁標題</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t xml:space="preserve">死線監獄 ｜ DEADLINE PRISON</t>
         </is>
       </c>
-      <c r="E155"/>
+      <c r="E162"/>
     </row>
   </sheetData>
 </worksheet>
@@ -12238,7 +12399,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12261,7 +12422,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">73</t>
+          <t xml:space="preserve">80</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12284,7 +12445,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">82</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -12307,7 +12468,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">86</t>
+          <t xml:space="preserve">87</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -12317,7 +12478,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次名不能空白</t>
+          <t xml:space="preserve">已開場，但密鑰設定失敗:</t>
         </is>
       </c>
       <c r="E22"/>
@@ -12330,17 +12491,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">102</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">提示</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">已更新場次</t>
+          <t xml:space="preserve">場次名不能空白</t>
         </is>
       </c>
       <c r="E23"/>
@@ -12353,17 +12514,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">92</t>
+          <t xml:space="preserve">107</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">編輯失敗，已還原:</t>
+          <t xml:space="preserve">已更新場次</t>
         </is>
       </c>
       <c r="E24"/>
@@ -12376,17 +12537,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">127</t>
+          <t xml:space="preserve">109</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態按鈕/成功</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">停止預約 / 已停止預約</t>
+          <t xml:space="preserve">編輯失敗，已還原:</t>
         </is>
       </c>
       <c r="E25"/>
@@ -12399,17 +12560,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">128</t>
+          <t xml:space="preserve">114</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態按鈕/成功</t>
+          <t xml:space="preserve">提示</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">開始入場 / 已開始入場</t>
+          <t xml:space="preserve">場次已更新，但密鑰設定失敗:</t>
         </is>
       </c>
       <c r="E26"/>
@@ -12422,7 +12583,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">132</t>
+          <t xml:space="preserve">150</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12432,7 +12593,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">恢復報名 / 已恢復報名</t>
+          <t xml:space="preserve">停止預約 / 已停止預約</t>
         </is>
       </c>
       <c r="E27"/>
@@ -12445,7 +12606,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">137</t>
+          <t xml:space="preserve">151</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12455,7 +12616,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">開始服刑 / 已開始服刑</t>
+          <t xml:space="preserve">開始入場 / 已開始入場</t>
         </is>
       </c>
       <c r="E28"/>
@@ -12468,7 +12629,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">138</t>
+          <t xml:space="preserve">155</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12478,7 +12639,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">退回停止預約 / 已退回停止預約</t>
+          <t xml:space="preserve">恢復報名 / 已恢復報名</t>
         </is>
       </c>
       <c r="E29"/>
@@ -12491,7 +12652,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">139</t>
+          <t xml:space="preserve">160</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12501,7 +12662,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">退回預約中 / 已退回預約中</t>
+          <t xml:space="preserve">開始服刑 / 已開始服刑</t>
         </is>
       </c>
       <c r="E30"/>
@@ -12514,17 +12675,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">143</t>
+          <t xml:space="preserve">161</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態按鈕/成功/confirm</t>
+          <t xml:space="preserve">狀態按鈕/成功</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">結束服刑 / 已結束服刑 / 確定結束本場服刑?結束後不可重開</t>
+          <t xml:space="preserve">退回停止預約 / 已退回停止預約</t>
         </is>
       </c>
       <c r="E31"/>
@@ -12537,17 +12698,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">144</t>
+          <t xml:space="preserve">162</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態按鈕/成功/confirm</t>
+          <t xml:space="preserve">狀態按鈕/成功</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">退回入場(清番茄鐘) / 已退回入場 / 將清掉番茄鐘計時、退回入場狀態，全場回到等待</t>
+          <t xml:space="preserve">退回預約中 / 已退回預約中</t>
         </is>
       </c>
       <c r="E32"/>
@@ -12560,17 +12721,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">166</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態文字</t>
+          <t xml:space="preserve">狀態按鈕/成功/confirm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">已結束</t>
+          <t xml:space="preserve">結束服刑 / 已結束服刑 / 確定結束本場服刑?結束後不可重開</t>
         </is>
       </c>
       <c r="E33"/>
@@ -12583,17 +12744,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">152</t>
+          <t xml:space="preserve">167</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">confirm</t>
+          <t xml:space="preserve">狀態按鈕/成功/confirm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">確定刪除場次「〈場次〉」?此動作無法復原，本場名單與目標也會一併移除</t>
+          <t xml:space="preserve">退回入場(清番茄鐘) / 已退回入場 / 將清掉番茄鐘計時、退回入場狀態，全場回到等待</t>
         </is>
       </c>
       <c r="E34"/>
@@ -12606,17 +12767,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">156</t>
+          <t xml:space="preserve">170</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">狀態文字</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">已刪除場次</t>
+          <t xml:space="preserve">已結束</t>
         </is>
       </c>
       <c r="E35"/>
@@ -12629,17 +12790,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">158</t>
+          <t xml:space="preserve">175</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">confirm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">刪除失敗，已還原:</t>
+          <t xml:space="preserve">確定刪除場次「〈場次〉」?此動作無法復原，本場名單與目標也會一併移除</t>
         </is>
       </c>
       <c r="E36"/>
@@ -12652,17 +12813,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">164</t>
+          <t xml:space="preserve">179</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">標題</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次總覽</t>
+          <t xml:space="preserve">已刪除場次</t>
         </is>
       </c>
       <c r="E37"/>
@@ -12675,17 +12836,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">168</t>
+          <t xml:space="preserve">181</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeholder</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次名(如 6/14 晚場)</t>
+          <t xml:space="preserve">刪除失敗，已還原:</t>
         </is>
       </c>
       <c r="E38"/>
@@ -12698,17 +12859,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">170</t>
+          <t xml:space="preserve">187</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeholder</t>
+          <t xml:space="preserve">標題</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">人數上限（留空＝不限）</t>
+          <t xml:space="preserve">場次總覽</t>
         </is>
       </c>
       <c r="E39"/>
@@ -12721,17 +12882,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">171</t>
+          <t xml:space="preserve">191</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">checkbox</t>
+          <t xml:space="preserve">placeholder</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">對外公開</t>
+          <t xml:space="preserve">場次名(如 6/14 晚場)</t>
         </is>
       </c>
       <c r="E40"/>
@@ -12744,17 +12905,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">172</t>
+          <t xml:space="preserve">193</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">placeholder</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">開新場次</t>
+          <t xml:space="preserve">人數上限（留空＝不限）</t>
         </is>
       </c>
       <c r="E41"/>
@@ -12767,17 +12928,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">175</t>
+          <t xml:space="preserve">194</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">載入中</t>
+          <t xml:space="preserve">checkbox</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">載入中…</t>
+          <t xml:space="preserve">對外公開</t>
         </is>
       </c>
       <c r="E42"/>
@@ -12790,17 +12951,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">176</t>
+          <t xml:space="preserve">196</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">placeholder</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">還沒有任何場次</t>
+          <t xml:space="preserve">通行密鑰（留空＝不設） /(內部場)內部場不可設密鑰</t>
         </is>
       </c>
       <c r="E43"/>
@@ -12813,17 +12974,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">188</t>
+          <t xml:space="preserve">198</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeholder</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">上限（留空＝不限）</t>
+          <t xml:space="preserve">開新場次</t>
         </is>
       </c>
       <c r="E44"/>
@@ -12836,17 +12997,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">190</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">載入中</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">儲存</t>
+          <t xml:space="preserve">載入中…</t>
         </is>
       </c>
       <c r="E45"/>
@@ -12859,17 +13020,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">191</t>
+          <t xml:space="preserve">202</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">取消</t>
+          <t xml:space="preserve">還沒有任何場次</t>
         </is>
       </c>
       <c r="E46"/>
@@ -12882,17 +13043,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">200</t>
+          <t xml:space="preserve">214</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">日期 fallback</t>
+          <t xml:space="preserve">placeholder</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">未設定日期</t>
+          <t xml:space="preserve">上限（留空＝不限）</t>
         </is>
       </c>
       <c r="E47"/>
@@ -12905,17 +13066,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">208</t>
+          <t xml:space="preserve">216</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">公開狀態</t>
+          <t xml:space="preserve">placeholder(編輯)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">官網公開 / 內部場</t>
+          <t xml:space="preserve">通行密鑰（留空＝不設） /(內部場)內部場不可設密鑰</t>
         </is>
       </c>
       <c r="E48"/>
@@ -12928,17 +13089,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">209</t>
+          <t xml:space="preserve">218</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">報到人數</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">報到 〈N〉 人</t>
+          <t xml:space="preserve">儲存</t>
         </is>
       </c>
       <c r="E49"/>
@@ -12951,17 +13112,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">210</t>
+          <t xml:space="preserve">219</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">上限顯示</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">上限 〈N〉(或 不限)</t>
+          <t xml:space="preserve">取消</t>
         </is>
       </c>
       <c r="E50"/>
@@ -12974,17 +13135,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">212</t>
+          <t xml:space="preserve">228</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">日期 fallback</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">編輯</t>
+          <t xml:space="preserve">未設定日期</t>
         </is>
       </c>
       <c r="E51"/>
@@ -12997,17 +13158,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">214</t>
+          <t xml:space="preserve">236</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">公開狀態</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">刪除</t>
+          <t xml:space="preserve">官網公開 / 內部場</t>
         </is>
       </c>
       <c r="E52"/>
@@ -13020,17 +13181,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">221</t>
+          <t xml:space="preserve">240</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">載入中</t>
+          <t xml:space="preserve">密鑰標記</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">讀取本場名單中…</t>
+          <t xml:space="preserve">密鑰:〈密鑰〉</t>
         </is>
       </c>
       <c r="E53"/>
@@ -13043,17 +13204,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">242</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">分組標題</t>
+          <t xml:space="preserve">報到人數</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場犯人 (〈N〉)</t>
+          <t xml:space="preserve">報到 〈N〉 人</t>
         </is>
       </c>
       <c r="E54"/>
@@ -13066,17 +13227,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">243</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">上限顯示</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場沒有犯人</t>
+          <t xml:space="preserve">上限 〈N〉(或 不限)</t>
         </is>
       </c>
       <c r="E55"/>
@@ -13089,17 +13250,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">245</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">名稱 fallback</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">(未知)</t>
+          <t xml:space="preserve">編輯</t>
         </is>
       </c>
       <c r="E56"/>
@@ -13112,17 +13273,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">239</t>
+          <t xml:space="preserve">247</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">分組標題</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場獄卒 (〈N〉)</t>
+          <t xml:space="preserve">刪除</t>
         </is>
       </c>
       <c r="E57"/>
@@ -13135,17 +13296,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">254</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">載入中</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場沒有獄卒</t>
+          <t xml:space="preserve">讀取本場名單中…</t>
         </is>
       </c>
       <c r="E58"/>
@@ -13158,17 +13319,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">250</t>
+          <t xml:space="preserve">255</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">角色標籤</t>
+          <t xml:space="preserve">分組標題</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">典獄長 / 獄卒</t>
+          <t xml:space="preserve">本場犯人 (〈N〉)</t>
         </is>
       </c>
       <c r="E59"/>
@@ -13176,22 +13337,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/SessionTab.jsx</t>
+          <t xml:space="preserve">src/warden/SessionsOverviewTab.jsx</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">256</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄鐘提示(booking)</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次預約中，尚未開始入場</t>
+          <t xml:space="preserve">本場沒有犯人</t>
         </is>
       </c>
       <c r="E60"/>
@@ -13199,22 +13360,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/SessionTab.jsx</t>
+          <t xml:space="preserve">src/warden/SessionsOverviewTab.jsx</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">264</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄鐘提示(paused)</t>
+          <t xml:space="preserve">名稱 fallback</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">已停止預約，尚未開始入場</t>
+          <t xml:space="preserve">(未知)</t>
         </is>
       </c>
       <c r="E61"/>
@@ -13222,22 +13383,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/SessionTab.jsx</t>
+          <t xml:space="preserve">src/warden/SessionsOverviewTab.jsx</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">272</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄鐘提示(intake)</t>
+          <t xml:space="preserve">分組標題</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">已開始入場，於「場次總覽」按『開始服刑』啟動番茄鐘</t>
+          <t xml:space="preserve">本場獄卒 (〈N〉)</t>
         </is>
       </c>
       <c r="E62"/>
@@ -13245,22 +13406,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/SessionTab.jsx</t>
+          <t xml:space="preserve">src/warden/SessionsOverviewTab.jsx</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">273</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄鐘提示(ended)</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場已結束</t>
+          <t xml:space="preserve">本場沒有獄卒</t>
         </is>
       </c>
       <c r="E63"/>
@@ -13268,22 +13429,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/SessionTab.jsx</t>
+          <t xml:space="preserve">src/warden/SessionsOverviewTab.jsx</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">104</t>
+          <t xml:space="preserve">283</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">角色標籤</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新失敗：〈error〉</t>
+          <t xml:space="preserve">典獄長 / 獄卒</t>
         </is>
       </c>
       <c r="E64"/>
@@ -13296,17 +13457,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">105</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">輪播切換提示</t>
+          <t xml:space="preserve">番茄鐘提示(booking)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">已恢復輪播 / 已標記完成，停止輪播</t>
+          <t xml:space="preserve">場次預約中，尚未開始入場</t>
         </is>
       </c>
       <c r="E65"/>
@@ -13319,17 +13480,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">提示</t>
+          <t xml:space="preserve">番茄鐘提示(paused)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">請選擇犯人、填寫探監者與廣播內容</t>
+          <t xml:space="preserve">已停止預約，尚未開始入場</t>
         </is>
       </c>
       <c r="E66"/>
@@ -13342,17 +13503,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">118</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">番茄鐘提示(intake)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">登錄探監失敗：〈error〉</t>
+          <t xml:space="preserve">已開始入場，於「場次總覽」按『開始服刑』啟動番茄鐘</t>
         </is>
       </c>
       <c r="E67"/>
@@ -13365,17 +13526,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">119</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">番茄鐘提示(ended)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">已登錄探監</t>
+          <t xml:space="preserve">本場已結束</t>
         </is>
       </c>
       <c r="E68"/>
@@ -13388,17 +13549,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">123</t>
+          <t xml:space="preserve">104</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">提示</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">探監者與內容不可空白</t>
+          <t xml:space="preserve">更新失敗：〈error〉</t>
         </is>
       </c>
       <c r="E69"/>
@@ -13411,17 +13572,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">127</t>
+          <t xml:space="preserve">105</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">輪播切換提示</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新探監失敗：〈error〉</t>
+          <t xml:space="preserve">已恢復輪播 / 已標記完成，停止輪播</t>
         </is>
       </c>
       <c r="E70"/>
@@ -13434,17 +13595,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">128</t>
+          <t xml:space="preserve">111</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">提示</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">已更新探監</t>
+          <t xml:space="preserve">請選擇犯人、填寫探監者與廣播內容</t>
         </is>
       </c>
       <c r="E71"/>
@@ -13457,17 +13618,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">132</t>
+          <t xml:space="preserve">118</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">confirm</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">確定刪除這筆探監？</t>
+          <t xml:space="preserve">登錄探監失敗：〈error〉</t>
         </is>
       </c>
       <c r="E72"/>
@@ -13480,17 +13641,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">134</t>
+          <t xml:space="preserve">119</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">刪除探監失敗：〈error〉</t>
+          <t xml:space="preserve">已登錄探監</t>
         </is>
       </c>
       <c r="E73"/>
@@ -13503,17 +13664,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">135</t>
+          <t xml:space="preserve">123</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">提示</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">已刪除探監</t>
+          <t xml:space="preserve">探監者與內容不可空白</t>
         </is>
       </c>
       <c r="E74"/>
@@ -13526,7 +13687,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">143</t>
+          <t xml:space="preserve">127</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -13536,7 +13697,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入目標失敗：〈error〉</t>
+          <t xml:space="preserve">更新探監失敗：〈error〉</t>
         </is>
       </c>
       <c r="E75"/>
@@ -13549,17 +13710,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">149</t>
+          <t xml:space="preserve">128</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">移除目標失敗：〈error〉</t>
+          <t xml:space="preserve">已更新探監</t>
         </is>
       </c>
       <c r="E76"/>
@@ -13572,7 +13733,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">158</t>
+          <t xml:space="preserve">132</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -13582,7 +13743,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">確定將這位犯人移出本場？</t>
+          <t xml:space="preserve">確定刪除這筆探監？</t>
         </is>
       </c>
       <c r="E77"/>
@@ -13595,7 +13756,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">160</t>
+          <t xml:space="preserve">134</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -13605,7 +13766,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">移出失敗：〈error〉</t>
+          <t xml:space="preserve">刪除探監失敗：〈error〉</t>
         </is>
       </c>
       <c r="E78"/>
@@ -13618,7 +13779,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">161</t>
+          <t xml:space="preserve">135</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -13628,7 +13789,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">已移出本場</t>
+          <t xml:space="preserve">已刪除探監</t>
         </is>
       </c>
       <c r="E79"/>
@@ -13641,7 +13802,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">174</t>
+          <t xml:space="preserve">143</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13651,7 +13812,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">子項目更新失敗，已還原：〈error〉</t>
+          <t xml:space="preserve">加入目標失敗：〈error〉</t>
         </is>
       </c>
       <c r="E80"/>
@@ -13664,17 +13825,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">149</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤(在別場)</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">〈名〉 還在其他未結束場次進行中，無法加入本場</t>
+          <t xml:space="preserve">移除目標失敗：〈error〉</t>
         </is>
       </c>
       <c r="E81"/>
@@ -13687,17 +13848,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">158</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">confirm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">〈名〉 加入失敗：〈error〉</t>
+          <t xml:space="preserve">確定將這位犯人移出本場？</t>
         </is>
       </c>
       <c r="E82"/>
@@ -13710,17 +13871,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">228</t>
+          <t xml:space="preserve">160</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">已加入 〈N〉 位本場獄卒</t>
+          <t xml:space="preserve">移出失敗：〈error〉</t>
         </is>
       </c>
       <c r="E83"/>
@@ -13733,17 +13894,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">237</t>
+          <t xml:space="preserve">161</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">帶入失敗：〈error〉</t>
+          <t xml:space="preserve">已移出本場</t>
         </is>
       </c>
       <c r="E84"/>
@@ -13756,17 +13917,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">252</t>
+          <t xml:space="preserve">174</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">標籤</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">目前場次</t>
+          <t xml:space="preserve">子項目更新失敗，已還原：〈error〉</t>
         </is>
       </c>
       <c r="E85"/>
@@ -13779,17 +13940,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">255</t>
+          <t xml:space="preserve">222</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">option</t>
+          <t xml:space="preserve">錯誤(在別場)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">— 選擇場次 —</t>
+          <t xml:space="preserve">〈名〉 還在其他未結束場次進行中，無法加入本場</t>
         </is>
       </c>
       <c r="E86"/>
@@ -13802,17 +13963,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">261</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">標籤</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">直播大螢幕</t>
+          <t xml:space="preserve">〈名〉 加入失敗：〈error〉</t>
         </is>
       </c>
       <c r="E87"/>
@@ -13825,17 +13986,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">264</t>
+          <t xml:space="preserve">228</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">無開放場次</t>
+          <t xml:space="preserve">已加入 〈N〉 位本場獄卒</t>
         </is>
       </c>
       <c r="E88"/>
@@ -13848,17 +14009,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">266</t>
+          <t xml:space="preserve">237</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">直播按鈕</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">📺 〈場次〉 ↗</t>
+          <t xml:space="preserve">帶入失敗：〈error〉</t>
         </is>
       </c>
       <c r="E89"/>
@@ -13871,7 +14032,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">278</t>
+          <t xml:space="preserve">252</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -13881,7 +14042,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄鐘</t>
+          <t xml:space="preserve">目前場次</t>
         </is>
       </c>
       <c r="E90"/>
@@ -13894,17 +14055,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">279</t>
+          <t xml:space="preserve">255</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄鐘提示 fallback</t>
+          <t xml:space="preserve">option</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場尚未開始服刑</t>
+          <t xml:space="preserve">— 選擇場次 —</t>
         </is>
       </c>
       <c r="E91"/>
@@ -13917,17 +14078,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">288</t>
+          <t xml:space="preserve">261</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">標題/說明</t>
+          <t xml:space="preserve">標籤</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場獄卒 / 手動新增獄卒</t>
+          <t xml:space="preserve">直播大螢幕</t>
         </is>
       </c>
       <c r="E92"/>
@@ -13940,7 +14101,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">291</t>
+          <t xml:space="preserve">264</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -13950,7 +14111,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">請先在上方選擇目前場次</t>
+          <t xml:space="preserve">無開放場次</t>
         </is>
       </c>
       <c r="E93"/>
@@ -13963,17 +14124,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">294</t>
+          <t xml:space="preserve">266</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeholder</t>
+          <t xml:space="preserve">直播按鈕</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">搜尋暱稱</t>
+          <t xml:space="preserve">📺 〈場次〉 ↗</t>
         </is>
       </c>
       <c r="E94"/>
@@ -13986,17 +14147,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">296</t>
+          <t xml:space="preserve">278</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">標籤</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">取消全選 / 全選</t>
+          <t xml:space="preserve">番茄鐘</t>
         </is>
       </c>
       <c r="E95"/>
@@ -14009,17 +14170,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">302</t>
+          <t xml:space="preserve">279</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">已選人數</t>
+          <t xml:space="preserve">番茄鐘提示 fallback</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">已選 〈N〉 人 →</t>
+          <t xml:space="preserve">本場尚未開始服刑</t>
         </is>
       </c>
       <c r="E96"/>
@@ -14032,17 +14193,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">303</t>
+          <t xml:space="preserve">288</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">標題/說明</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入為本場獄卒</t>
+          <t xml:space="preserve">本場獄卒 / 手動新增獄卒</t>
         </is>
       </c>
       <c r="E97"/>
@@ -14055,7 +14216,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">308</t>
+          <t xml:space="preserve">291</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -14065,7 +14226,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">沒有可加入的獄卒（名單中沒有符合的人選，或搜尋無結果）</t>
+          <t xml:space="preserve">請先在上方選擇目前場次</t>
         </is>
       </c>
       <c r="E98"/>
@@ -14078,17 +14239,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">318</t>
+          <t xml:space="preserve">294</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態文字</t>
+          <t xml:space="preserve">placeholder</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">已在場</t>
+          <t xml:space="preserve">搜尋暱稱</t>
         </is>
       </c>
       <c r="E99"/>
@@ -14101,7 +14262,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">319</t>
+          <t xml:space="preserve">296</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -14111,7 +14272,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">加入</t>
+          <t xml:space="preserve">取消全選 / 全選</t>
         </is>
       </c>
       <c r="E100"/>
@@ -14124,17 +14285,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">324</t>
+          <t xml:space="preserve">302</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">說明文字</t>
+          <t xml:space="preserve">已選人數</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">名單僅列出獄卒／典獄長身分的人員；犯人會在「開始入場」時自動帶入，也可用右側「重新帶入預約名單」補上。</t>
+          <t xml:space="preserve">已選 〈N〉 人 →</t>
         </is>
       </c>
       <c r="E101"/>
@@ -14147,17 +14308,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">303</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">標題</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場名單</t>
+          <t xml:space="preserve">加入為本場獄卒</t>
         </is>
       </c>
       <c r="E102"/>
@@ -14170,17 +14331,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">308</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">重新帶入預約名單</t>
+          <t xml:space="preserve">沒有可加入的獄卒（名單中沒有符合的人選，或搜尋無結果）</t>
         </is>
       </c>
       <c r="E103"/>
@@ -14193,17 +14354,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">336</t>
+          <t xml:space="preserve">318</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">載入中</t>
+          <t xml:space="preserve">狀態文字</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">載入中…</t>
+          <t xml:space="preserve">已在場</t>
         </is>
       </c>
       <c r="E104"/>
@@ -14216,17 +14377,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">337</t>
+          <t xml:space="preserve">319</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場還沒有人</t>
+          <t xml:space="preserve">加入</t>
         </is>
       </c>
       <c r="E105"/>
@@ -14239,17 +14400,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">324</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">分組標題</t>
+          <t xml:space="preserve">說明文字</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場犯人 (〈N〉)</t>
+          <t xml:space="preserve">名單僅列出獄卒／典獄長身分的人員；犯人會在「開始入場」時自動帶入，也可用右側「重新帶入預約名單」補上。</t>
         </is>
       </c>
       <c r="E106"/>
@@ -14262,17 +14423,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">342</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">標題</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場沒有犯人</t>
+          <t xml:space="preserve">本場名單</t>
         </is>
       </c>
       <c r="E107"/>
@@ -14285,17 +14446,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">350</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人編號</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">No.〈編號〉</t>
+          <t xml:space="preserve">重新帶入預約名單</t>
         </is>
       </c>
       <c r="E108"/>
@@ -14308,17 +14469,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">351</t>
+          <t xml:space="preserve">336</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人狀態</t>
+          <t xml:space="preserve">載入中</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">（〈狀態〉）</t>
+          <t xml:space="preserve">載入中…</t>
         </is>
       </c>
       <c r="E109"/>
@@ -14331,17 +14492,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">353</t>
+          <t xml:space="preserve">337</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">移出本場</t>
+          <t xml:space="preserve">本場還沒有人</t>
         </is>
       </c>
       <c r="E110"/>
@@ -14354,17 +14515,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">358</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">欄位標籤</t>
+          <t xml:space="preserve">分組標題</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場目標</t>
+          <t xml:space="preserve">本場犯人 (〈N〉)</t>
         </is>
       </c>
       <c r="E111"/>
@@ -14377,7 +14538,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">360</t>
+          <t xml:space="preserve">342</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -14387,7 +14548,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">尚未挑選</t>
+          <t xml:space="preserve">本場沒有犯人</t>
         </is>
       </c>
       <c r="E112"/>
@@ -14400,17 +14561,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">369</t>
+          <t xml:space="preserve">350</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">犯人編號</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">收合 / 展開</t>
+          <t xml:space="preserve">No.〈編號〉</t>
         </is>
       </c>
       <c r="E113"/>
@@ -14423,17 +14584,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">370</t>
+          <t xml:space="preserve">351</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">犯人狀態</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">移除</t>
+          <t xml:space="preserve">（〈狀態〉）</t>
         </is>
       </c>
       <c r="E114"/>
@@ -14446,17 +14607,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">375</t>
+          <t xml:space="preserve">353</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">這本稿還沒有子項目</t>
+          <t xml:space="preserve">移出本場</t>
         </is>
       </c>
       <c r="E115"/>
@@ -14469,17 +14630,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">388</t>
+          <t xml:space="preserve">358</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">欄位標籤</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">+ 新增本場目標</t>
+          <t xml:space="preserve">本場目標</t>
         </is>
       </c>
       <c r="E116"/>
@@ -14492,17 +14653,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">395</t>
+          <t xml:space="preserve">360</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">欄位標籤</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">專屬獄卒</t>
+          <t xml:space="preserve">尚未挑選</t>
         </is>
       </c>
       <c r="E117"/>
@@ -14515,17 +14676,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">404</t>
+          <t xml:space="preserve">369</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">分組標題</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場獄卒 (〈N〉)</t>
+          <t xml:space="preserve">收合 / 展開</t>
         </is>
       </c>
       <c r="E118"/>
@@ -14538,17 +14699,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">405</t>
+          <t xml:space="preserve">370</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場沒有獄卒</t>
+          <t xml:space="preserve">移除</t>
         </is>
       </c>
       <c r="E119"/>
@@ -14561,17 +14722,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">409</t>
+          <t xml:space="preserve">375</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">移出本場</t>
+          <t xml:space="preserve">這本稿還沒有子項目</t>
         </is>
       </c>
       <c r="E120"/>
@@ -14584,17 +14745,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">388</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">名稱首字 fallback</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">?</t>
+          <t xml:space="preserve">+ 新增本場目標</t>
         </is>
       </c>
       <c r="E121"/>
@@ -14607,17 +14768,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">416</t>
+          <t xml:space="preserve">395</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">角色標籤</t>
+          <t xml:space="preserve">欄位標籤</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">典獄長 / 獄卒</t>
+          <t xml:space="preserve">專屬獄卒</t>
         </is>
       </c>
       <c r="E122"/>
@@ -14630,17 +14791,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">430</t>
+          <t xml:space="preserve">404</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">標題/筆數</t>
+          <t xml:space="preserve">分組標題</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">探監登錄 / 〈N〉 筆</t>
+          <t xml:space="preserve">本場獄卒 (〈N〉)</t>
         </is>
       </c>
       <c r="E123"/>
@@ -14653,17 +14814,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">405</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">option</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">— 選擇犯人 —</t>
+          <t xml:space="preserve">本場沒有獄卒</t>
         </is>
       </c>
       <c r="E124"/>
@@ -14676,17 +14837,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">437</t>
+          <t xml:space="preserve">409</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">option</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">No.〈編號〉 〈名字〉</t>
+          <t xml:space="preserve">移出本場</t>
         </is>
       </c>
       <c r="E125"/>
@@ -14699,17 +14860,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">442</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">option</t>
+          <t xml:space="preserve">名稱首字 fallback</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">— 指定獄卒（選填）—</t>
+          <t xml:space="preserve">?</t>
         </is>
       </c>
       <c r="E126"/>
@@ -14722,17 +14883,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">445</t>
+          <t xml:space="preserve">416</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">option 標註</t>
+          <t xml:space="preserve">角色標籤</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">（典獄長）</t>
+          <t xml:space="preserve">典獄長 / 獄卒</t>
         </is>
       </c>
       <c r="E127"/>
@@ -14745,17 +14906,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">449</t>
+          <t xml:space="preserve">430</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeholder</t>
+          <t xml:space="preserve">標題/筆數</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">探監者名字</t>
+          <t xml:space="preserve">探監登錄 / 〈N〉 筆</t>
         </is>
       </c>
       <c r="E128"/>
@@ -14768,17 +14929,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">452</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeholder</t>
+          <t xml:space="preserve">option</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">廣播內容（最多 80 字）</t>
+          <t xml:space="preserve">— 選擇犯人 —</t>
         </is>
       </c>
       <c r="E129"/>
@@ -14791,17 +14952,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">454</t>
+          <t xml:space="preserve">437</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">字數計數</t>
+          <t xml:space="preserve">option</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">〈N〉 / 80</t>
+          <t xml:space="preserve">No.〈編號〉 〈名字〉</t>
         </is>
       </c>
       <c r="E130"/>
@@ -14814,17 +14975,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">456</t>
+          <t xml:space="preserve">442</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">option</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">送出探監</t>
+          <t xml:space="preserve">— 指定獄卒（選填）—</t>
         </is>
       </c>
       <c r="E131"/>
@@ -14837,17 +14998,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">460</t>
+          <t xml:space="preserve">445</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">option 標註</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">本場還沒有探監紀錄</t>
+          <t xml:space="preserve">（典獄長）</t>
         </is>
       </c>
       <c r="E132"/>
@@ -14860,17 +15021,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">466</t>
+          <t xml:space="preserve">449</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">名稱 fallback(犯人)</t>
+          <t xml:space="preserve">placeholder</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">（已離場）</t>
+          <t xml:space="preserve">探監者名字</t>
         </is>
       </c>
       <c r="E133"/>
@@ -14883,17 +15044,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">467</t>
+          <t xml:space="preserve">452</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">名稱 fallback(獄卒)</t>
+          <t xml:space="preserve">placeholder</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">（已離場）</t>
+          <t xml:space="preserve">廣播內容（最多 80 字）</t>
         </is>
       </c>
       <c r="E134"/>
@@ -14906,17 +15067,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">473</t>
+          <t xml:space="preserve">454</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeholder(編輯)</t>
+          <t xml:space="preserve">字數計數</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">探監者</t>
+          <t xml:space="preserve">〈N〉 / 80</t>
         </is>
       </c>
       <c r="E135"/>
@@ -14929,17 +15090,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">477</t>
+          <t xml:space="preserve">456</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">option(編輯)</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">— 指定獄卒（選填）—</t>
+          <t xml:space="preserve">送出探監</t>
         </is>
       </c>
       <c r="E136"/>
@@ -14952,17 +15113,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">480</t>
+          <t xml:space="preserve">460</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">option 標註(編輯)</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">（典獄長）</t>
+          <t xml:space="preserve">本場還沒有探監紀錄</t>
         </is>
       </c>
       <c r="E137"/>
@@ -14975,17 +15136,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">484</t>
+          <t xml:space="preserve">466</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeholder(編輯)</t>
+          <t xml:space="preserve">名稱 fallback(犯人)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">內容</t>
+          <t xml:space="preserve">（已離場）</t>
         </is>
       </c>
       <c r="E138"/>
@@ -14998,17 +15159,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">487</t>
+          <t xml:space="preserve">467</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕(編輯)</t>
+          <t xml:space="preserve">名稱 fallback(獄卒)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">取消</t>
+          <t xml:space="preserve">（已離場）</t>
         </is>
       </c>
       <c r="E139"/>
@@ -15021,17 +15182,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">488</t>
+          <t xml:space="preserve">473</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕(編輯)</t>
+          <t xml:space="preserve">placeholder(編輯)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">儲存</t>
+          <t xml:space="preserve">探監者</t>
         </is>
       </c>
       <c r="E140"/>
@@ -15044,17 +15205,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">495</t>
+          <t xml:space="preserve">477</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">探監列顯示</t>
+          <t xml:space="preserve">option(編輯)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">💌 〈探監者〉 → No.〈編號〉 〈犯人〉</t>
+          <t xml:space="preserve">— 指定獄卒（選填）—</t>
         </is>
       </c>
       <c r="E141"/>
@@ -15067,17 +15228,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">496</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">已完成標記</t>
+          <t xml:space="preserve">option 標註(編輯)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">✓ 已完成</t>
+          <t xml:space="preserve">（典獄長）</t>
         </is>
       </c>
       <c r="E142"/>
@@ -15090,17 +15251,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">498</t>
+          <t xml:space="preserve">484</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">探監內容</t>
+          <t xml:space="preserve">placeholder(編輯)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">「〈內容〉」</t>
+          <t xml:space="preserve">內容</t>
         </is>
       </c>
       <c r="E143"/>
@@ -15113,17 +15274,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">499</t>
+          <t xml:space="preserve">487</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">指定獄卒顯示</t>
+          <t xml:space="preserve">按鈕(編輯)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">🛡 指定獄卒：〈獄卒名〉</t>
+          <t xml:space="preserve">取消</t>
         </is>
       </c>
       <c r="E144"/>
@@ -15136,17 +15297,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">503</t>
+          <t xml:space="preserve">488</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">按鈕(編輯)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">恢復輪播 / 標記完成</t>
+          <t xml:space="preserve">儲存</t>
         </is>
       </c>
       <c r="E145"/>
@@ -15159,17 +15320,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">504</t>
+          <t xml:space="preserve">495</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">探監列顯示</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">編輯</t>
+          <t xml:space="preserve">💌 〈探監者〉 → No.〈編號〉 〈犯人〉</t>
         </is>
       </c>
       <c r="E146"/>
@@ -15182,17 +15343,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">505</t>
+          <t xml:space="preserve">496</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">已完成標記</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">刪除</t>
+          <t xml:space="preserve">✓ 已完成</t>
         </is>
       </c>
       <c r="E147"/>
@@ -15205,17 +15366,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">529</t>
+          <t xml:space="preserve">498</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">modal 標題</t>
+          <t xml:space="preserve">探監內容</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">新增本場目標 · 〈名〉</t>
+          <t xml:space="preserve">「〈內容〉」</t>
         </is>
       </c>
       <c r="E148"/>
@@ -15228,17 +15389,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">534</t>
+          <t xml:space="preserve">499</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">指定獄卒顯示</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">沒有可以加入的稿件，請到「我的稿件」新增</t>
+          <t xml:space="preserve">🛡 指定獄卒：〈獄卒名〉</t>
         </is>
       </c>
       <c r="E149"/>
@@ -15251,7 +15412,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">536</t>
+          <t xml:space="preserve">503</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -15261,7 +15422,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">前往我的稿件</t>
+          <t xml:space="preserve">恢復輪播 / 標記完成</t>
         </is>
       </c>
       <c r="E150"/>
@@ -15274,7 +15435,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">544</t>
+          <t xml:space="preserve">504</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -15284,7 +15445,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">＋ 加入</t>
+          <t xml:space="preserve">編輯</t>
         </is>
       </c>
       <c r="E151"/>
@@ -15292,22 +15453,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/BookingsTab.jsx</t>
+          <t xml:space="preserve">src/warden/SessionTab.jsx</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">505</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態標籤</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">待確認</t>
+          <t xml:space="preserve">刪除</t>
         </is>
       </c>
       <c r="E152"/>
@@ -15315,22 +15476,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/BookingsTab.jsx</t>
+          <t xml:space="preserve">src/warden/SessionTab.jsx</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態標籤</t>
+          <t xml:space="preserve">modal 標題</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">已確認</t>
+          <t xml:space="preserve">新增本場目標 · 〈名〉</t>
         </is>
       </c>
       <c r="E153"/>
@@ -15338,22 +15499,22 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/BookingsTab.jsx</t>
+          <t xml:space="preserve">src/warden/SessionTab.jsx</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">534</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態標籤</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">已取消</t>
+          <t xml:space="preserve">沒有可以加入的稿件，請到「我的稿件」新增</t>
         </is>
       </c>
       <c r="E154"/>
@@ -15361,22 +15522,22 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/BookingsTab.jsx</t>
+          <t xml:space="preserve">src/warden/SessionTab.jsx</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">536</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">confirm</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">確定將這筆預約改為「已取消」?</t>
+          <t xml:space="preserve">前往我的稿件</t>
         </is>
       </c>
       <c r="E155"/>
@@ -15384,22 +15545,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/BookingsTab.jsx</t>
+          <t xml:space="preserve">src/warden/SessionTab.jsx</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">544</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新狀態失敗，已還原:</t>
+          <t xml:space="preserve">＋ 加入</t>
         </is>
       </c>
       <c r="E156"/>
@@ -15412,17 +15573,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">狀態標籤</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">已更新預約狀態</t>
+          <t xml:space="preserve">待確認</t>
         </is>
       </c>
       <c r="E157"/>
@@ -15435,17 +15596,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">69</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">狀態標籤</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新預約資料失敗，已還原:</t>
+          <t xml:space="preserve">已確認</t>
         </is>
       </c>
       <c r="E158"/>
@@ -15458,17 +15619,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">狀態標籤</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">已更新預約暱稱/頭像</t>
+          <t xml:space="preserve">已取消</t>
         </is>
       </c>
       <c r="E159"/>
@@ -15481,17 +15642,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">標題</t>
+          <t xml:space="preserve">confirm</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">預約總覽</t>
+          <t xml:space="preserve">確定將這筆預約改為「已取消」?</t>
         </is>
       </c>
       <c r="E160"/>
@@ -15504,17 +15665,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">載入中</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">載入中…</t>
+          <t xml:space="preserve">更新狀態失敗，已還原:</t>
         </is>
       </c>
       <c r="E161"/>
@@ -15527,17 +15688,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">空狀態</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">目前沒有任何預約</t>
+          <t xml:space="preserve">已更新預約狀態</t>
         </is>
       </c>
       <c r="E162"/>
@@ -15550,17 +15711,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">86</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">日期 fallback</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">未定</t>
+          <t xml:space="preserve">更新預約資料失敗，已還原:</t>
         </is>
       </c>
       <c r="E163"/>
@@ -15573,17 +15734,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">89</t>
+          <t xml:space="preserve">71</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態標籤</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">進行中 / 已結束</t>
+          <t xml:space="preserve">已更新預約暱稱/頭像</t>
         </is>
       </c>
       <c r="E164"/>
@@ -15596,17 +15757,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">已預約人數</t>
+          <t xml:space="preserve">標題</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">已預約 〈N〉</t>
+          <t xml:space="preserve">預約總覽</t>
         </is>
       </c>
       <c r="E165"/>
@@ -15619,17 +15780,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">102</t>
+          <t xml:space="preserve">76</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">顯示</t>
+          <t xml:space="preserve">載入中</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">暱稱:</t>
+          <t xml:space="preserve">載入中…</t>
         </is>
       </c>
       <c r="E166"/>
@@ -15642,17 +15803,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">103</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">顯示</t>
+          <t xml:space="preserve">空狀態</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC:</t>
+          <t xml:space="preserve">目前沒有任何預約</t>
         </is>
       </c>
       <c r="E167"/>
@@ -15665,17 +15826,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">104</t>
+          <t xml:space="preserve">86</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">顯示</t>
+          <t xml:space="preserve">日期 fallback</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">備註:</t>
+          <t xml:space="preserve">未定</t>
         </is>
       </c>
       <c r="E168"/>
@@ -15688,17 +15849,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">108</t>
+          <t xml:space="preserve">89</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">狀態標籤</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">編輯暱稱/頭像</t>
+          <t xml:space="preserve">進行中 / 已結束</t>
         </is>
       </c>
       <c r="E169"/>
@@ -15711,17 +15872,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">109</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">已預約人數</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">確認</t>
+          <t xml:space="preserve">已預約 〈N〉</t>
         </is>
       </c>
       <c r="E170"/>
@@ -15734,17 +15895,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">110</t>
+          <t xml:space="preserve">102</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">顯示</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">改待確認</t>
+          <t xml:space="preserve">暱稱:</t>
         </is>
       </c>
       <c r="E171"/>
@@ -15757,17 +15918,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">103</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">顯示</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">取消</t>
+          <t xml:space="preserve">DC:</t>
         </is>
       </c>
       <c r="E172"/>
@@ -15780,17 +15941,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">125</t>
+          <t xml:space="preserve">104</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">modal 標題</t>
+          <t xml:space="preserve">顯示</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">編輯預約暱稱/頭像</t>
+          <t xml:space="preserve">備註:</t>
         </is>
       </c>
       <c r="E173"/>
@@ -15803,17 +15964,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">126</t>
+          <t xml:space="preserve">108</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">暱稱</t>
+          <t xml:space="preserve">編輯暱稱/頭像</t>
         </is>
       </c>
       <c r="E174"/>
@@ -15826,17 +15987,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">130</t>
+          <t xml:space="preserve">109</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">欄位標籤</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">頭像</t>
+          <t xml:space="preserve">確認</t>
         </is>
       </c>
       <c r="E175"/>
@@ -15849,7 +16010,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">134</t>
+          <t xml:space="preserve">110</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -15859,7 +16020,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">取消</t>
+          <t xml:space="preserve">改待確認</t>
         </is>
       </c>
       <c r="E176"/>
@@ -15872,7 +16033,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">135</t>
+          <t xml:space="preserve">111</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -15882,7 +16043,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">儲存</t>
+          <t xml:space="preserve">取消</t>
         </is>
       </c>
       <c r="E177"/>
@@ -15890,22 +16051,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/GuardAssign.jsx</t>
+          <t xml:space="preserve">src/warden/BookingsTab.jsx</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">125</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">modal 標題</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">指派失敗:</t>
+          <t xml:space="preserve">編輯預約暱稱/頭像</t>
         </is>
       </c>
       <c r="E178"/>
@@ -15913,22 +16074,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/GuardAssign.jsx</t>
+          <t xml:space="preserve">src/warden/BookingsTab.jsx</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">126</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">移除指派失敗:</t>
+          <t xml:space="preserve">暱稱</t>
         </is>
       </c>
       <c r="E179"/>
@@ -15936,22 +16097,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/GuardAssign.jsx</t>
+          <t xml:space="preserve">src/warden/BookingsTab.jsx</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">130</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態文字</t>
+          <t xml:space="preserve">欄位標籤</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">未指派</t>
+          <t xml:space="preserve">頭像</t>
         </is>
       </c>
       <c r="E180"/>
@@ -15959,22 +16120,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/GuardAssign.jsx</t>
+          <t xml:space="preserve">src/warden/BookingsTab.jsx</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">134</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">角色標籤</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">典獄長 / 獄卒</t>
+          <t xml:space="preserve">取消</t>
         </is>
       </c>
       <c r="E181"/>
@@ -15982,22 +16143,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/GuardAssign.jsx</t>
+          <t xml:space="preserve">src/warden/BookingsTab.jsx</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">135</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">option</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">— 指派專屬獄卒 —</t>
+          <t xml:space="preserve">儲存</t>
         </is>
       </c>
       <c r="E182"/>
@@ -16010,17 +16171,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">64</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">指派</t>
+          <t xml:space="preserve">指派失敗:</t>
         </is>
       </c>
       <c r="E183"/>
@@ -16033,17 +16194,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">65</t>
+          <t xml:space="preserve">41</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">提示文字</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">(本場尚無獄卒可指派)</t>
+          <t xml:space="preserve">移除指派失敗:</t>
         </is>
       </c>
       <c r="E184"/>
@@ -16051,22 +16212,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/EditMemberModal.jsx</t>
+          <t xml:space="preserve">src/warden/GuardAssign.jsx</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">狀態文字</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">儲存失敗:〈訊息〉(若是改身分，僅典獄長可變更)</t>
+          <t xml:space="preserve">未指派</t>
         </is>
       </c>
       <c r="E185"/>
@@ -16074,22 +16235,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/EditMemberModal.jsx</t>
+          <t xml:space="preserve">src/warden/GuardAssign.jsx</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">角色標籤</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">儲存失敗:編號需為正整數</t>
+          <t xml:space="preserve">典獄長 / 獄卒</t>
         </is>
       </c>
       <c r="E186"/>
@@ -16097,22 +16258,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/EditMemberModal.jsx</t>
+          <t xml:space="preserve">src/warden/GuardAssign.jsx</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">option</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">儲存失敗:</t>
+          <t xml:space="preserve">— 指派專屬獄卒 —</t>
         </is>
       </c>
       <c r="E187"/>
@@ -16120,22 +16281,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/EditMemberModal.jsx</t>
+          <t xml:space="preserve">src/warden/GuardAssign.jsx</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">64</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功(改身分)</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">已儲存。已將身分變更為「〈身分〉」，該使用者需「重新登入」才會生效</t>
+          <t xml:space="preserve">指派</t>
         </is>
       </c>
       <c r="E188"/>
@@ -16143,22 +16304,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/EditMemberModal.jsx</t>
+          <t xml:space="preserve">src/warden/GuardAssign.jsx</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">65</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">提示文字</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">已儲存犯人資料</t>
+          <t xml:space="preserve">(本場尚無獄卒可指派)</t>
         </is>
       </c>
       <c r="E189"/>
@@ -16171,17 +16332,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">modal 標題</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">編輯犯人資料</t>
+          <t xml:space="preserve">儲存失敗:〈訊息〉(若是改身分，僅典獄長可變更)</t>
         </is>
       </c>
       <c r="E190"/>
@@ -16194,17 +16355,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">編號 No.</t>
+          <t xml:space="preserve">儲存失敗:編號需為正整數</t>
         </is>
       </c>
       <c r="E191"/>
@@ -16217,17 +16378,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">49</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">遊戲暱稱</t>
+          <t xml:space="preserve">儲存失敗:</t>
         </is>
       </c>
       <c r="E192"/>
@@ -16240,17 +16401,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">欄位標籤</t>
+          <t xml:space="preserve">成功(改身分)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">頭像</t>
+          <t xml:space="preserve">已儲存。已將身分變更為「〈身分〉」，該使用者需「重新登入」才會生效</t>
         </is>
       </c>
       <c r="E193"/>
@@ -16263,17 +16424,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Discord 帳號</t>
+          <t xml:space="preserve">已儲存犯人資料</t>
         </is>
       </c>
       <c r="E194"/>
@@ -16286,17 +16447,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">modal 標題</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">身分 role</t>
+          <t xml:space="preserve">編輯犯人資料</t>
         </is>
       </c>
       <c r="E195"/>
@@ -16309,17 +16470,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">option</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人</t>
+          <t xml:space="preserve">編號 No.</t>
         </is>
       </c>
       <c r="E196"/>
@@ -16332,17 +16493,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">49</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">option</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">獄卒</t>
+          <t xml:space="preserve">遊戲暱稱</t>
         </is>
       </c>
       <c r="E197"/>
@@ -16355,17 +16516,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">63</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">option</t>
+          <t xml:space="preserve">欄位標籤</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">典獄長</t>
+          <t xml:space="preserve">頭像</t>
         </is>
       </c>
       <c r="E198"/>
@@ -16378,17 +16539,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">67</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">警告文字</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ 變更身分後，該使用者需重新登入才會生效</t>
+          <t xml:space="preserve">Discord 帳號</t>
         </is>
       </c>
       <c r="E199"/>
@@ -16401,17 +16562,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">取消</t>
+          <t xml:space="preserve">身分 role</t>
         </is>
       </c>
       <c r="E200"/>
@@ -16424,17 +16585,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">option</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">儲存</t>
+          <t xml:space="preserve">犯人</t>
         </is>
       </c>
       <c r="E201"/>
@@ -16442,22 +16603,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/SessionTimerControl.jsx</t>
+          <t xml:space="preserve">src/warden/EditMemberModal.jsx</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">confirm</t>
+          <t xml:space="preserve">option</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">確定結束本場服刑?結束後不可重開</t>
+          <t xml:space="preserve">獄卒</t>
         </is>
       </c>
       <c r="E202"/>
@@ -16465,22 +16626,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/SessionTimerControl.jsx</t>
+          <t xml:space="preserve">src/warden/EditMemberModal.jsx</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">option</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">結束失敗:</t>
+          <t xml:space="preserve">典獄長</t>
         </is>
       </c>
       <c r="E203"/>
@@ -16488,22 +16649,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/SessionTimerControl.jsx</t>
+          <t xml:space="preserve">src/warden/EditMemberModal.jsx</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">67</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">警告文字</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">已結束服刑</t>
+          <t xml:space="preserve">⚠️ 變更身分後，該使用者需重新登入才會生效</t>
         </is>
       </c>
       <c r="E204"/>
@@ -16511,22 +16672,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/SessionTimerControl.jsx</t>
+          <t xml:space="preserve">src/warden/EditMemberModal.jsx</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">70</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">confirm</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">將清掉番茄鐘計時、退回入場狀態，全場回到等待</t>
+          <t xml:space="preserve">取消</t>
         </is>
       </c>
       <c r="E205"/>
@@ -16534,22 +16695,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/SessionTimerControl.jsx</t>
+          <t xml:space="preserve">src/warden/EditMemberModal.jsx</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">71</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">退回入場失敗:</t>
+          <t xml:space="preserve">儲存</t>
         </is>
       </c>
       <c r="E206"/>
@@ -16562,17 +16723,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">confirm</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">已退回入場</t>
+          <t xml:space="preserve">確定結束本場服刑?結束後不可重開</t>
         </is>
       </c>
       <c r="E207"/>
@@ -16585,17 +16746,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">提示</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">不能少於目前進行中的輪數</t>
+          <t xml:space="preserve">結束失敗:</t>
         </is>
       </c>
       <c r="E208"/>
@@ -16608,17 +16769,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">錯誤</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">調整輪數失敗:</t>
+          <t xml:space="preserve">已結束服刑</t>
         </is>
       </c>
       <c r="E209"/>
@@ -16631,17 +16792,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">成功</t>
+          <t xml:space="preserve">confirm</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">已 ±1 輪，現為 〈N〉 輪</t>
+          <t xml:space="preserve">將清掉番茄鐘計時、退回入場狀態，全場回到等待</t>
         </is>
       </c>
       <c r="E210"/>
@@ -16654,17 +16815,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t xml:space="preserve">38</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄鐘標籤</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">番茄鐘</t>
+          <t xml:space="preserve">退回入場失敗:</t>
         </is>
       </c>
       <c r="E211"/>
@@ -16677,17 +16838,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態文字</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">● 服刑中 · 第 〈n〉 輪 / 共 〈N〉 輪</t>
+          <t xml:space="preserve">已退回入場</t>
         </is>
       </c>
       <c r="E212"/>
@@ -16700,17 +16861,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">提示</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">＋輪</t>
+          <t xml:space="preserve">不能少於目前進行中的輪數</t>
         </is>
       </c>
       <c r="E213"/>
@@ -16723,17 +16884,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">78</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">錯誤</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">−輪</t>
+          <t xml:space="preserve">調整輪數失敗:</t>
         </is>
       </c>
       <c r="E214"/>
@@ -16746,17 +16907,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">80</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">開始時間</t>
+          <t xml:space="preserve">成功</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">開始於 〈時間〉</t>
+          <t xml:space="preserve">已 ±1 輪，現為 〈N〉 輪</t>
         </is>
       </c>
       <c r="E215"/>
@@ -16769,17 +16930,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">83</t>
+          <t xml:space="preserve">74</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">番茄鐘標籤</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">提早結束 /(busy)處理中…</t>
+          <t xml:space="preserve">番茄鐘</t>
         </is>
       </c>
       <c r="E216"/>
@@ -16792,17 +16953,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">84</t>
+          <t xml:space="preserve">76</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">狀態文字</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">退回入場 /(busy)處理中…</t>
+          <t xml:space="preserve">● 服刑中 · 第 〈n〉 輪 / 共 〈N〉 輪</t>
         </is>
       </c>
       <c r="E217"/>
@@ -16815,17 +16976,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">94</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態文字</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">🔓 本場服刑結束(收尾中，請按下方『結束服刑』)</t>
+          <t xml:space="preserve">＋輪</t>
         </is>
       </c>
       <c r="E218"/>
@@ -16838,7 +16999,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">97</t>
+          <t xml:space="preserve">78</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -16848,7 +17009,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">結束服刑 /(busy)處理中…</t>
+          <t xml:space="preserve">−輪</t>
         </is>
       </c>
       <c r="E219"/>
@@ -16861,17 +17022,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">98</t>
+          <t xml:space="preserve">80</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">按鈕</t>
+          <t xml:space="preserve">開始時間</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">退回入場(清番茄鐘) /(busy)處理中…</t>
+          <t xml:space="preserve">開始於 〈時間〉</t>
         </is>
       </c>
       <c r="E220"/>
@@ -16884,17 +17045,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">107</t>
+          <t xml:space="preserve">83</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">狀態文字</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">計時未啟動</t>
+          <t xml:space="preserve">提早結束 /(busy)處理中…</t>
         </is>
       </c>
       <c r="E221"/>
@@ -16902,22 +17063,22 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/constants.js</t>
+          <t xml:space="preserve">src/warden/SessionTimerControl.jsx</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">84</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">角色對照 label</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">犯人 / 獄卒 / 典獄長</t>
+          <t xml:space="preserve">退回入場 /(busy)處理中…</t>
         </is>
       </c>
       <c r="E222"/>
@@ -16925,22 +17086,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/constants.js</t>
+          <t xml:space="preserve">src/warden/SessionTimerControl.jsx</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">94</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">帶入跳過提示</t>
+          <t xml:space="preserve">狀態文字</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">〈名〉 還在場次「〈場次〉」，無法帶入本場</t>
+          <t xml:space="preserve">🔓 本場服刑結束(收尾中，請按下方『結束服刑』)</t>
         </is>
       </c>
       <c r="E223"/>
@@ -16948,22 +17109,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/constants.js</t>
+          <t xml:space="preserve">src/warden/SessionTimerControl.jsx</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">97</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">帶入成功提示</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">已帶入預約名單</t>
+          <t xml:space="preserve">結束服刑 /(busy)處理中…</t>
         </is>
       </c>
       <c r="E224"/>
@@ -16971,22 +17132,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/constants.js</t>
+          <t xml:space="preserve">src/warden/SessionTimerControl.jsx</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">98</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次狀態 label</t>
+          <t xml:space="preserve">按鈕</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">預約中</t>
+          <t xml:space="preserve">退回入場(清番茄鐘) /(busy)處理中…</t>
         </is>
       </c>
       <c r="E225"/>
@@ -16994,22 +17155,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">src/warden/constants.js</t>
+          <t xml:space="preserve">src/warden/SessionTimerControl.jsx</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">107</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次狀態 label</t>
+          <t xml:space="preserve">狀態文字</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">停止預約</t>
+          <t xml:space="preserve">計時未啟動</t>
         </is>
       </c>
       <c r="E226"/>
@@ -17022,17 +17183,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次狀態 label</t>
+          <t xml:space="preserve">角色對照 label</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">開始入場</t>
+          <t xml:space="preserve">犯人 / 獄卒 / 典獄長</t>
         </is>
       </c>
       <c r="E227"/>
@@ -17045,17 +17206,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次狀態 label</t>
+          <t xml:space="preserve">帶入跳過提示</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑中</t>
+          <t xml:space="preserve">〈名〉 還在場次「〈場次〉」，無法帶入本場</t>
         </is>
       </c>
       <c r="E228"/>
@@ -17068,17 +17229,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">場次狀態 label</t>
+          <t xml:space="preserve">帶入成功提示</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">已結束</t>
+          <t xml:space="preserve">已帶入預約名單</t>
         </is>
       </c>
       <c r="E229"/>
@@ -17091,17 +17252,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">總覽狀態</t>
+          <t xml:space="preserve">場次狀態 label</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑中</t>
+          <t xml:space="preserve">預約中</t>
         </is>
       </c>
       <c r="E230"/>
@@ -17114,17 +17275,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">總覽狀態</t>
+          <t xml:space="preserve">場次狀態 label</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">放風</t>
+          <t xml:space="preserve">停止預約</t>
         </is>
       </c>
       <c r="E231"/>
@@ -17137,17 +17298,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">總覽狀態</t>
+          <t xml:space="preserve">場次狀態 label</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">長休息</t>
+          <t xml:space="preserve">開始入場</t>
         </is>
       </c>
       <c r="E232"/>
@@ -17160,17 +17321,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">總覽狀態</t>
+          <t xml:space="preserve">場次狀態 label</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">在場待命</t>
+          <t xml:space="preserve">服刑中</t>
         </is>
       </c>
       <c r="E233"/>
@@ -17183,12 +17344,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">總覽狀態</t>
+          <t xml:space="preserve">場次狀態 label</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -17206,7 +17367,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -17216,7 +17377,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">不在場</t>
+          <t xml:space="preserve">服刑中</t>
         </is>
       </c>
       <c r="E235"/>
@@ -17229,17 +17390,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">成員狀態</t>
+          <t xml:space="preserve">總覽狀態</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">不在場</t>
+          <t xml:space="preserve">放風</t>
         </is>
       </c>
       <c r="E236"/>
@@ -17252,17 +17413,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">成員狀態</t>
+          <t xml:space="preserve">總覽狀態</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">在場待命</t>
+          <t xml:space="preserve">長休息</t>
         </is>
       </c>
       <c r="E237"/>
@@ -17275,20 +17436,135 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
+          <t xml:space="preserve">36</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">總覽狀態</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在場待命</t>
+        </is>
+      </c>
+      <c r="E238"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/warden/constants.js</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">總覽狀態</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已結束</t>
+        </is>
+      </c>
+      <c r="E239"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/warden/constants.js</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">總覽狀態</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不在場</t>
+        </is>
+      </c>
+      <c r="E240"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/warden/constants.js</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">成員狀態</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不在場</t>
+        </is>
+      </c>
+      <c r="E241"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/warden/constants.js</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">成員狀態</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">在場待命</t>
+        </is>
+      </c>
+      <c r="E242"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/warden/constants.js</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
           <t xml:space="preserve">47</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t xml:space="preserve">成員狀態(ended)</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t xml:space="preserve">已結束</t>
         </is>
       </c>
-      <c r="E238"/>
+      <c r="E243"/>
     </row>
   </sheetData>
 </worksheet>

--- a/文案總表.xlsx
+++ b/文案總表.xlsx
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">125</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">121</t>
+          <t xml:space="preserve">126</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">199</t>
+          <t xml:space="preserve">219</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200</t>
+          <t xml:space="preserve">220</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">218</t>
+          <t xml:space="preserve">238</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">219</t>
+          <t xml:space="preserve">239</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">220</t>
+          <t xml:space="preserve">240</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">221</t>
+          <t xml:space="preserve">241</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">222</t>
+          <t xml:space="preserve">242</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">243</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">252</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">236</t>
+          <t xml:space="preserve">256</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">242</t>
+          <t xml:space="preserve">262</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">246</t>
+          <t xml:space="preserve">266</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">258</t>
+          <t xml:space="preserve">278</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">260</t>
+          <t xml:space="preserve">280</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">261</t>
+          <t xml:space="preserve">281</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">262</t>
+          <t xml:space="preserve">282</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">263</t>
+          <t xml:space="preserve">283</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">264</t>
+          <t xml:space="preserve">284</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">265</t>
+          <t xml:space="preserve">285</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">268</t>
+          <t xml:space="preserve">288</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">269</t>
+          <t xml:space="preserve">289</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">278</t>
+          <t xml:space="preserve">298</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">293</t>
+          <t xml:space="preserve">313</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">293</t>
+          <t xml:space="preserve">313</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">293</t>
+          <t xml:space="preserve">313</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">294</t>
+          <t xml:space="preserve">314</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">294</t>
+          <t xml:space="preserve">314</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">294</t>
+          <t xml:space="preserve">314</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">304</t>
+          <t xml:space="preserve">324</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">305</t>
+          <t xml:space="preserve">325</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">326</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">307</t>
+          <t xml:space="preserve">327</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">308</t>
+          <t xml:space="preserve">328</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">309</t>
+          <t xml:space="preserve">329</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">310</t>
+          <t xml:space="preserve">330</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">314</t>
+          <t xml:space="preserve">334</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">316</t>
+          <t xml:space="preserve">336</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">323</t>
+          <t xml:space="preserve">343</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">324</t>
+          <t xml:space="preserve">344</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">325</t>
+          <t xml:space="preserve">345</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">326</t>
+          <t xml:space="preserve">346</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">353</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">339</t>
+          <t xml:space="preserve">359</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">340</t>
+          <t xml:space="preserve">360</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">361</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">350</t>
+          <t xml:space="preserve">370</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">351</t>
+          <t xml:space="preserve">371</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">352</t>
+          <t xml:space="preserve">372</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t xml:space="preserve">354</t>
+          <t xml:space="preserve">374</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">362</t>
+          <t xml:space="preserve">382</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">373</t>
+          <t xml:space="preserve">393</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">374</t>
+          <t xml:space="preserve">394</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">375</t>
+          <t xml:space="preserve">395</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">377</t>
+          <t xml:space="preserve">396</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">378</t>
+          <t xml:space="preserve">397</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2685,17 +2685,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">398</t>
+          <t xml:space="preserve">400</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·eyebrow</t>
+          <t xml:space="preserve">犯人牆·收容人數</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">監獄名人堂 // BLOCK 04</t>
+          <t xml:space="preserve">收容人數 〈N〉 人</t>
         </is>
       </c>
       <c r="E114"/>
@@ -2708,17 +2708,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">399</t>
+          <t xml:space="preserve">403</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·標題</t>
+          <t xml:space="preserve">犯人牆·翻頁 aria</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂</t>
+          <t xml:space="preserve">上一頁</t>
         </is>
       </c>
       <c r="E115"/>
@@ -2731,17 +2731,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">400</t>
+          <t xml:space="preserve">406</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·說明</t>
+          <t xml:space="preserve">犯人牆·頁碼</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑最勤、人氣最高的犯人。次數照實計入，名字是否公開由本人決定。</t>
+          <t xml:space="preserve">〈目前頁〉 / 〈總頁數〉</t>
         </is>
       </c>
       <c r="E116"/>
@@ -2754,17 +2754,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">403</t>
+          <t xml:space="preserve">407</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·榜一</t>
+          <t xml:space="preserve">犯人牆·翻頁 aria</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">慣犯榜 — 入監次數 TOP 10</t>
+          <t xml:space="preserve">下一頁</t>
         </is>
       </c>
       <c r="E117"/>
@@ -2777,17 +2777,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">404</t>
+          <t xml:space="preserve">440</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·榜二</t>
+          <t xml:space="preserve">名人堂·eyebrow</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">人氣榜 — 收到探監 TOP 10</t>
+          <t xml:space="preserve">監獄名人堂 // BLOCK 04</t>
         </is>
       </c>
       <c r="E118"/>
@@ -2800,17 +2800,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">411</t>
+          <t xml:space="preserve">441</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·空狀態</t>
+          <t xml:space="preserve">名人堂·標題</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">名冊整備中…</t>
+          <t xml:space="preserve">名人堂</t>
         </is>
       </c>
       <c r="E119"/>
@@ -2823,17 +2823,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">419</t>
+          <t xml:space="preserve">442</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·隱名</t>
+          <t xml:space="preserve">名人堂·說明</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">〔機密犯人〕</t>
+          <t xml:space="preserve">服刑最勤、人氣最高的犯人。次數照實計入，名字是否公開由本人決定。</t>
         </is>
       </c>
       <c r="E120"/>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">420</t>
+          <t xml:space="preserve">445</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·第一名徽章</t>
+          <t xml:space="preserve">名人堂·榜一</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">重刑犯</t>
+          <t xml:space="preserve">慣犯榜 — 入監次數 TOP 10</t>
         </is>
       </c>
       <c r="E121"/>
@@ -2869,17 +2869,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">446</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">名人堂·次數後綴</t>
+          <t xml:space="preserve">名人堂·榜二</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">〈數字〉 次</t>
+          <t xml:space="preserve">人氣榜 — 收到探監 TOP 10</t>
         </is>
       </c>
       <c r="E122"/>
@@ -2892,17 +2892,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">436</t>
+          <t xml:space="preserve">453</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·eyebrow</t>
+          <t xml:space="preserve">名人堂·空狀態</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">營業項目 // BLOCK 05</t>
+          <t xml:space="preserve">名冊整備中…</t>
         </is>
       </c>
       <c r="E123"/>
@@ -2915,17 +2915,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">437</t>
+          <t xml:space="preserve">461</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·標題</t>
+          <t xml:space="preserve">名人堂·隱名</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目</t>
+          <t xml:space="preserve">〔機密犯人〕</t>
         </is>
       </c>
       <c r="E124"/>
@@ -2938,17 +2938,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">438</t>
+          <t xml:space="preserve">462</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·說明</t>
+          <t xml:space="preserve">名人堂·第一名徽章</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">把自己關起來也要明碼標價。保釋金制度為增加體驗之設計，非強制消費；所有互動皆為角色扮演，請保持良好的 RP 禮儀。</t>
+          <t xml:space="preserve">重刑犯</t>
         </is>
       </c>
       <c r="E125"/>
@@ -2961,17 +2961,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">456</t>
+          <t xml:space="preserve">464</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·保釋金標題</t>
+          <t xml:space="preserve">名人堂·次數後綴</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">保釋金退還規則</t>
+          <t xml:space="preserve">〈數字〉 次</t>
         </is>
       </c>
       <c r="E126"/>
@@ -2984,17 +2984,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">469</t>
+          <t xml:space="preserve">478</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">收費價目·加購標題</t>
+          <t xml:space="preserve">收費價目·eyebrow</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">加購項目 // ADD-ON</t>
+          <t xml:space="preserve">營業項目 // BLOCK 05</t>
         </is>
       </c>
       <c r="E127"/>
@@ -3007,17 +3007,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">485</t>
+          <t xml:space="preserve">479</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·eyebrow</t>
+          <t xml:space="preserve">收費價目·標題</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑梯次 // BLOCK 06</t>
+          <t xml:space="preserve">收費價目</t>
         </is>
       </c>
       <c r="E128"/>
@@ -3030,17 +3030,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">486</t>
+          <t xml:space="preserve">480</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·標題</t>
+          <t xml:space="preserve">收費價目·說明</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">近期趕稿場次</t>
+          <t xml:space="preserve">把自己關起來也要明碼標價。保釋金制度為增加體驗之設計，非強制消費；所有互動皆為角色扮演，請保持良好的 RP 禮儀。</t>
         </is>
       </c>
       <c r="E129"/>
@@ -3053,17 +3053,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">487</t>
+          <t xml:space="preserve">498</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·說明</t>
+          <t xml:space="preserve">收費價目·保釋金標題</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">選一個梯次自首入監。額滿停止收監，過期梯次已結案。</t>
+          <t xml:space="preserve">保釋金退還規則</t>
         </is>
       </c>
       <c r="E130"/>
@@ -3076,17 +3076,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">489</t>
+          <t xml:space="preserve">511</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·載入中</t>
+          <t xml:space="preserve">收費價目·加購標題</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">調閱梯次中…</t>
+          <t xml:space="preserve">加購項目 // ADD-ON</t>
         </is>
       </c>
       <c r="E131"/>
@@ -3099,17 +3099,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">490</t>
+          <t xml:space="preserve">527</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·空狀態</t>
+          <t xml:space="preserve">趕稿場次·eyebrow</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">目前沒有開放收監的梯次</t>
+          <t xml:space="preserve">服刑梯次 // BLOCK 06</t>
         </is>
       </c>
       <c r="E132"/>
@@ -3122,17 +3122,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">498</t>
+          <t xml:space="preserve">528</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·人數</t>
+          <t xml:space="preserve">趕稿場次·標題</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">已報名 〈X〉 / 〈Y〉 / 已報名 〈X〉 人</t>
+          <t xml:space="preserve">近期趕稿場次</t>
         </is>
       </c>
       <c r="E133"/>
@@ -3145,17 +3145,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">512</t>
+          <t xml:space="preserve">529</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·入監按鈕</t>
+          <t xml:space="preserve">趕稿場次·說明</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監服刑 /(密鑰場)密鑰入獄</t>
+          <t xml:space="preserve">選一個梯次自首入監。額滿停止收監，過期梯次已結案。</t>
         </is>
       </c>
       <c r="E134"/>
@@ -3168,17 +3168,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">514</t>
+          <t xml:space="preserve">531</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">趕稿場次·按鈕(額滿/狀態)</t>
+          <t xml:space="preserve">趕稿場次·載入中</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">已額滿 / 〈狀態〉</t>
+          <t xml:space="preserve">調閱梯次中…</t>
         </is>
       </c>
       <c r="E135"/>
@@ -3191,17 +3191,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">524</t>
+          <t xml:space="preserve">532</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·品牌</t>
+          <t xml:space="preserve">趕稿場次·空狀態</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">死線監獄</t>
+          <t xml:space="preserve">目前沒有開放收監的梯次</t>
         </is>
       </c>
       <c r="E136"/>
@@ -3214,17 +3214,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">525</t>
+          <t xml:space="preserve">540</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·副標</t>
+          <t xml:space="preserve">趕稿場次·人數</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEADLINE PRISON · 趕稿收容所 · since 2026</t>
+          <t xml:space="preserve">已報名 〈X〉 / 〈Y〉 / 已報名 〈X〉 人</t>
         </is>
       </c>
       <c r="E137"/>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">526</t>
+          <t xml:space="preserve">554</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·地址</t>
+          <t xml:space="preserve">趕稿場次·入監按鈕</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑地點：巴哈姆特 - 薰衣草苗園 - 1區 - 18號</t>
+          <t xml:space="preserve">入監服刑 /(密鑰場)密鑰入獄</t>
         </is>
       </c>
       <c r="E138"/>
@@ -3260,17 +3260,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">527</t>
+          <t xml:space="preserve">556</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">頁尾·結案章</t>
+          <t xml:space="preserve">趕稿場次·按鈕(額滿/狀態)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">結案 · CLASSIFIED</t>
+          <t xml:space="preserve">已額滿 / 〈狀態〉</t>
         </is>
       </c>
       <c r="E139"/>
@@ -3283,17 +3283,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">536</t>
+          <t xml:space="preserve">566</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·關閉</t>
+          <t xml:space="preserve">頁尾·品牌</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">✕</t>
+          <t xml:space="preserve">死線監獄</t>
         </is>
       </c>
       <c r="E140"/>
@@ -3306,17 +3306,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">538</t>
+          <t xml:space="preserve">567</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·eyebrow</t>
+          <t xml:space="preserve">頁尾·副標</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監服刑 · INTAKE /(密鑰場)密鑰入獄 · INTAKE</t>
+          <t xml:space="preserve">DEADLINE PRISON · 趕稿收容所 · since 2026</t>
         </is>
       </c>
       <c r="E141"/>
@@ -3329,17 +3329,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">540</t>
+          <t xml:space="preserve">568</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位</t>
+          <t xml:space="preserve">頁尾·地址</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">梯次編號</t>
+          <t xml:space="preserve">服刑地點：巴哈姆特 - 薰衣草苗園 - 1區 - 18號</t>
         </is>
       </c>
       <c r="E142"/>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">541</t>
+          <t xml:space="preserve">569</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位(日期未定)</t>
+          <t xml:space="preserve">頁尾·結案章</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑日期 /(未定)</t>
+          <t xml:space="preserve">結案 · CLASSIFIED</t>
         </is>
       </c>
       <c r="E143"/>
@@ -3375,17 +3375,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">542</t>
+          <t xml:space="preserve">578</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位(不限)</t>
+          <t xml:space="preserve">Modal·關閉</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">收容情況 / 〈X〉 ／ 不限</t>
+          <t xml:space="preserve">✕</t>
         </is>
       </c>
       <c r="E144"/>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">548</t>
+          <t xml:space="preserve">580</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·未登入說明</t>
+          <t xml:space="preserve">Modal·eyebrow</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監採 Discord 登入，登入後自動帶入你的 DC 身分作為服刑名冊紀錄，無需另填聯絡方式。</t>
+          <t xml:space="preserve">入監服刑 · INTAKE /(密鑰場)密鑰入獄 · INTAKE</t>
         </is>
       </c>
       <c r="E145"/>
@@ -3421,17 +3421,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">549</t>
+          <t xml:space="preserve">582</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·按鈕</t>
+          <t xml:space="preserve">Modal·欄位</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">以 Discord 登入入監</t>
+          <t xml:space="preserve">梯次編號</t>
         </is>
       </c>
       <c r="E146"/>
@@ -3444,17 +3444,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">553</t>
+          <t xml:space="preserve">583</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·已報名說明</t>
+          <t xml:space="preserve">Modal·欄位(日期未定)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">你已在此梯次服刑名冊上。</t>
+          <t xml:space="preserve">服刑日期 /(未定)</t>
         </is>
       </c>
       <c r="E147"/>
@@ -3467,17 +3467,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">554</t>
+          <t xml:space="preserve">584</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·按鈕</t>
+          <t xml:space="preserve">Modal·欄位(不限)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">取消預約</t>
+          <t xml:space="preserve">收容情況 / 〈X〉 ／ 不限</t>
         </is>
       </c>
       <c r="E148"/>
@@ -3490,17 +3490,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">559</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·密鑰場說明</t>
+          <t xml:space="preserve">Modal·未登入說明</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">本梯次為密鑰場，請輸入通行密鑰後繼續報名。</t>
+          <t xml:space="preserve">入監採 Discord 登入，登入後自動帶入你的 DC 身分作為服刑名冊紀錄，無需另填聯絡方式。</t>
         </is>
       </c>
       <c r="E149"/>
@@ -3513,17 +3513,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">561</t>
+          <t xml:space="preserve">591</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">通行密鑰</t>
+          <t xml:space="preserve">以 Discord 登入入監</t>
         </is>
       </c>
       <c r="E150"/>
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">562</t>
+          <t xml:space="preserve">595</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·placeholder</t>
+          <t xml:space="preserve">Modal·已報名說明</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">輸入通行密鑰</t>
+          <t xml:space="preserve">你已在此梯次服刑名冊上。</t>
         </is>
       </c>
       <c r="E151"/>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">568</t>
+          <t xml:space="preserve">596</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">核對中… / 核對密鑰</t>
+          <t xml:space="preserve">取消預約</t>
         </is>
       </c>
       <c r="E152"/>
@@ -3582,17 +3582,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">573</t>
+          <t xml:space="preserve">601</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·已取消說明</t>
+          <t xml:space="preserve">Modal·密鑰場說明</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">你先前已取消此梯次。要重新登記入監名冊嗎？</t>
+          <t xml:space="preserve">本梯次為密鑰場，請輸入通行密鑰後繼續報名。</t>
         </is>
       </c>
       <c r="E153"/>
@@ -3605,17 +3605,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">574</t>
+          <t xml:space="preserve">603</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·按鈕</t>
+          <t xml:space="preserve">Modal·欄位</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">處理中… / 重新報名</t>
+          <t xml:space="preserve">通行密鑰</t>
         </is>
       </c>
       <c r="E154"/>
@@ -3628,17 +3628,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">581</t>
+          <t xml:space="preserve">604</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·沿用身分說明</t>
+          <t xml:space="preserve">Modal·placeholder</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">以 〈暱稱〉 身分入監，確認後登入服刑名冊。</t>
+          <t xml:space="preserve">輸入通行密鑰</t>
         </is>
       </c>
       <c r="E155"/>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">583</t>
+          <t xml:space="preserve">610</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">收監中… / 確認入監</t>
+          <t xml:space="preserve">核對中… / 核對密鑰</t>
         </is>
       </c>
       <c r="E156"/>
@@ -3674,17 +3674,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">588</t>
+          <t xml:space="preserve">615</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·補填說明</t>
+          <t xml:space="preserve">Modal·已取消說明</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">入監前請設定你的服刑暱稱與頭像（將作為本梯次名冊的顯示資料）。</t>
+          <t xml:space="preserve">你先前已取消此梯次。要重新登記入監名冊嗎？</t>
         </is>
       </c>
       <c r="E157"/>
@@ -3697,17 +3697,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">590</t>
+          <t xml:space="preserve">616</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">服刑暱稱（必填）</t>
+          <t xml:space="preserve">處理中… / 重新報名</t>
         </is>
       </c>
       <c r="E158"/>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">591</t>
+          <t xml:space="preserve">623</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·placeholder</t>
+          <t xml:space="preserve">Modal·沿用身分說明</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">顯示在名冊上的暱稱</t>
+          <t xml:space="preserve">以 〈暱稱〉 身分入監，確認後登入服刑名冊。</t>
         </is>
       </c>
       <c r="E159"/>
@@ -3743,17 +3743,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">594</t>
+          <t xml:space="preserve">625</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·欄位</t>
+          <t xml:space="preserve">Modal·按鈕</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">頭像</t>
+          <t xml:space="preserve">收監中… / 確認入監</t>
         </is>
       </c>
       <c r="E160"/>
@@ -3766,17 +3766,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">598</t>
+          <t xml:space="preserve">630</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modal·按鈕</t>
+          <t xml:space="preserve">Modal·補填說明</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">收監中… / 確認入監</t>
+          <t xml:space="preserve">入監前請設定你的服刑暱稱與頭像（將作為本梯次名冊的顯示資料）。</t>
         </is>
       </c>
       <c r="E161"/>
@@ -3784,25 +3784,117 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">632</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·欄位</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">服刑暱稱（必填）</t>
+        </is>
+      </c>
+      <c r="E162"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">633</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·placeholder</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">顯示在名冊上的暱稱</t>
+        </is>
+      </c>
+      <c r="E163"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">636</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·欄位</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">頭像</t>
+        </is>
+      </c>
+      <c r="E164"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">src/site/PrisonSite.jsx</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modal·按鈕</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">收監中… / 確認入監</t>
+        </is>
+      </c>
+      <c r="E165"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t xml:space="preserve">index.html</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B166" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t xml:space="preserve">瀏覽器分頁標題</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t xml:space="preserve">死線監獄 ｜ DEADLINE PRISON</t>
         </is>
       </c>
-      <c r="E162"/>
+      <c r="E166"/>
     </row>
   </sheetData>
 </worksheet>
